--- a/model/Outputs/11. Interest rate/0/Output Files/0.3/Output_6_37.xlsx
+++ b/model/Outputs/11. Interest rate/0/Output Files/0.3/Output_6_37.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1989871.841627037</v>
+        <v>1982089.72262471</v>
       </c>
     </row>
     <row r="7">
@@ -506,7 +506,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7154817.030747599</v>
+        <v>7552736.626707198</v>
       </c>
     </row>
     <row r="8">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7154817.030747599</v>
+        <v>7552736.626707198</v>
       </c>
     </row>
     <row r="9">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1421810.501097731</v>
+        <v>1235723.121316086</v>
       </c>
     </row>
     <row r="10">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1421810.501097731</v>
+        <v>1235723.121316086</v>
       </c>
     </row>
     <row r="11">
@@ -556,7 +556,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>17696398.62559231</v>
+        <v>17761018.47209024</v>
       </c>
     </row>
   </sheetData>
@@ -675,7 +675,7 @@
         <v>8.009658703527407</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>28.70619138541446</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -705,7 +705,7 @@
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>123.5543591877376</v>
+        <v>94.84816780232291</v>
       </c>
       <c r="T2" t="n">
         <v>186.6755817285639</v>
@@ -736,7 +736,7 @@
         <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>141.7804375265674</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -745,16 +745,16 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>140.7678969571885</v>
       </c>
       <c r="G3" t="n">
-        <v>325.7395358750273</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>332.1680871864211</v>
       </c>
       <c r="I3" t="n">
-        <v>217.1263858913485</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -778,7 +778,7 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>173.0792650904796</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
         <v>147.2737972923793</v>
@@ -790,7 +790,7 @@
         <v>5.357765217513816</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2103597601867477</v>
+        <v>385</v>
       </c>
       <c r="V3" t="n">
         <v>14.51066719152016</v>
@@ -842,7 +842,7 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>23.54762815777917</v>
+        <v>21.95645751172319</v>
       </c>
       <c r="M4" t="n">
         <v>120.6316114025499</v>
@@ -860,7 +860,7 @@
         <v>325.839266425598</v>
       </c>
       <c r="R4" t="n">
-        <v>325.0109573350953</v>
+        <v>326.6021279811511</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -909,7 +909,7 @@
         <v>3.75737228701621</v>
       </c>
       <c r="H5" t="n">
-        <v>36.71585008894188</v>
+        <v>8.009658703527407</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -945,7 +945,7 @@
         <v>94.84816780232291</v>
       </c>
       <c r="T5" t="n">
-        <v>186.6755817285639</v>
+        <v>215.3817731139785</v>
       </c>
       <c r="U5" t="n">
         <v>249.2212965486107</v>
@@ -976,22 +976,22 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>192.3498461705186</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G6" t="n">
-        <v>308.4311513056531</v>
+        <v>325.7395358750273</v>
       </c>
       <c r="H6" t="n">
-        <v>332.1680871864211</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>217.1263858913485</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1079,7 +1079,7 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>23.54762815777917</v>
+        <v>21.95645751172319</v>
       </c>
       <c r="M7" t="n">
         <v>120.6316114025499</v>
@@ -1097,7 +1097,7 @@
         <v>325.839266425598</v>
       </c>
       <c r="R7" t="n">
-        <v>325.0109573350953</v>
+        <v>326.6021279811511</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1228,7 +1228,7 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>217.1263858913485</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>147.2737972923793</v>
+        <v>249.9535322209957</v>
       </c>
       <c r="S9" t="n">
         <v>66.5639999646113</v>
@@ -1267,7 +1267,7 @@
         <v>0.2103597601867477</v>
       </c>
       <c r="V9" t="n">
-        <v>14.51066719152016</v>
+        <v>385</v>
       </c>
       <c r="W9" t="n">
         <v>32.37314290982852</v>
@@ -1276,7 +1276,7 @@
         <v>19.86273944538755</v>
       </c>
       <c r="Y9" t="n">
-        <v>256.0426818457476</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1316,7 +1316,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>23.54762815777917</v>
+        <v>21.95645751172319</v>
       </c>
       <c r="M10" t="n">
         <v>120.6316114025499</v>
@@ -1334,7 +1334,7 @@
         <v>325.839266425598</v>
       </c>
       <c r="R10" t="n">
-        <v>325.0109573350953</v>
+        <v>326.6021279811511</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -1365,25 +1365,25 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>256.9993129555745</v>
+        <v>230.9993129555745</v>
       </c>
       <c r="C11" t="n">
-        <v>224.4745782429939</v>
+        <v>198.4745782429939</v>
       </c>
       <c r="D11" t="n">
-        <v>185.3391557398498</v>
+        <v>159.3391557398498</v>
       </c>
       <c r="E11" t="n">
-        <v>179.3632896068686</v>
+        <v>153.3632896068686</v>
       </c>
       <c r="F11" t="n">
-        <v>179.8896287080119</v>
+        <v>153.8896287080119</v>
       </c>
       <c r="G11" t="n">
-        <v>178.7573722870162</v>
+        <v>152.7573722870162</v>
       </c>
       <c r="H11" t="n">
-        <v>183.0096587035274</v>
+        <v>157.0096587035274</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -1413,28 +1413,28 @@
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>31.37179138541422</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>269.8481678023229</v>
+        <v>243.8481678023229</v>
       </c>
       <c r="T11" t="n">
-        <v>361.6755817285639</v>
+        <v>335.6755817285639</v>
       </c>
       <c r="U11" t="n">
-        <v>424.2212965486107</v>
+        <v>398.2212965486107</v>
       </c>
       <c r="V11" t="n">
-        <v>404.8510241668239</v>
+        <v>378.8510241668239</v>
       </c>
       <c r="W11" t="n">
-        <v>413.3734759809475</v>
+        <v>390.7844673663619</v>
       </c>
       <c r="X11" t="n">
-        <v>367.2818334606677</v>
+        <v>341.2818334606677</v>
       </c>
       <c r="Y11" t="n">
-        <v>286.3174326828064</v>
+        <v>260.3174326828064</v>
       </c>
     </row>
     <row r="12">
@@ -1444,25 +1444,25 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>159.5565566463266</v>
+        <v>133.5565566463266</v>
       </c>
       <c r="C12" t="n">
-        <v>136.0999124455193</v>
+        <v>110.0999124455193</v>
       </c>
       <c r="D12" t="n">
-        <v>122.9376868977026</v>
+        <v>96.93768689770263</v>
       </c>
       <c r="E12" t="n">
-        <v>117.6720972219126</v>
+        <v>91.67209722191262</v>
       </c>
       <c r="F12" t="n">
-        <v>114.6362423378769</v>
+        <v>88.63624233787687</v>
       </c>
       <c r="G12" t="n">
-        <v>100.7395358750273</v>
+        <v>74.73953587502734</v>
       </c>
       <c r="H12" t="n">
-        <v>107.1680871864211</v>
+        <v>81.16808718642113</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
@@ -1492,28 +1492,28 @@
         <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>322.2737972923793</v>
+        <v>296.2737972923793</v>
       </c>
       <c r="S12" t="n">
-        <v>241.5639999646113</v>
+        <v>215.5639999646113</v>
       </c>
       <c r="T12" t="n">
-        <v>180.3577652175138</v>
+        <v>154.3577652175138</v>
       </c>
       <c r="U12" t="n">
-        <v>175.2103597601867</v>
+        <v>149.2103597601867</v>
       </c>
       <c r="V12" t="n">
-        <v>189.5106671915202</v>
+        <v>163.5106671915202</v>
       </c>
       <c r="W12" t="n">
-        <v>207.3731429098285</v>
+        <v>181.3731429098285</v>
       </c>
       <c r="X12" t="n">
-        <v>194.8627394453875</v>
+        <v>168.8627394453875</v>
       </c>
       <c r="Y12" t="n">
-        <v>174.3913927661343</v>
+        <v>148.3913927661343</v>
       </c>
     </row>
     <row r="13">
@@ -1526,13 +1526,13 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>47.72524664804467</v>
+        <v>0</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>55.98090483695654</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>3.77112610161862</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -1553,10 +1553,10 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>172.5476281577792</v>
       </c>
       <c r="M13" t="n">
-        <v>237.0706480035264</v>
+        <v>269.6316114025499</v>
       </c>
       <c r="N13" t="n">
         <v>0</v>
@@ -1568,7 +1568,7 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>49.93595474591677</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -1586,13 +1586,13 @@
         <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.372809838709685</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>36.46535284946236</v>
       </c>
     </row>
     <row r="14">
@@ -1602,25 +1602,25 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>256.9993129555745</v>
+        <v>230.9993129555745</v>
       </c>
       <c r="C14" t="n">
-        <v>224.4745782429939</v>
+        <v>198.4745782429939</v>
       </c>
       <c r="D14" t="n">
-        <v>185.3391557398498</v>
+        <v>159.3391557398498</v>
       </c>
       <c r="E14" t="n">
-        <v>179.3632896068686</v>
+        <v>153.3632896068686</v>
       </c>
       <c r="F14" t="n">
-        <v>179.8896287080119</v>
+        <v>153.8896287080119</v>
       </c>
       <c r="G14" t="n">
-        <v>178.7573722870162</v>
+        <v>152.7573722870162</v>
       </c>
       <c r="H14" t="n">
-        <v>183.0096587035274</v>
+        <v>157.0096587035274</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -1650,28 +1650,28 @@
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>31.37179138541422</v>
+        <v>3.41099138541414</v>
       </c>
       <c r="S14" t="n">
-        <v>269.8481678023229</v>
+        <v>243.8481678023229</v>
       </c>
       <c r="T14" t="n">
-        <v>361.6755817285639</v>
+        <v>335.6755817285639</v>
       </c>
       <c r="U14" t="n">
-        <v>424.2212965486107</v>
+        <v>398.2212965486107</v>
       </c>
       <c r="V14" t="n">
-        <v>404.8510241668239</v>
+        <v>378.8510241668239</v>
       </c>
       <c r="W14" t="n">
-        <v>413.3734759809475</v>
+        <v>387.3734759809475</v>
       </c>
       <c r="X14" t="n">
-        <v>367.2818334606677</v>
+        <v>341.2818334606677</v>
       </c>
       <c r="Y14" t="n">
-        <v>286.3174326828064</v>
+        <v>260.3174326828064</v>
       </c>
     </row>
     <row r="15">
@@ -1681,25 +1681,25 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>159.5565566463266</v>
+        <v>133.5565566463266</v>
       </c>
       <c r="C15" t="n">
-        <v>136.0999124455193</v>
+        <v>110.0999124455193</v>
       </c>
       <c r="D15" t="n">
-        <v>122.9376868977026</v>
+        <v>96.93768689770263</v>
       </c>
       <c r="E15" t="n">
-        <v>117.6720972219126</v>
+        <v>91.67209722191262</v>
       </c>
       <c r="F15" t="n">
-        <v>114.6362423378769</v>
+        <v>88.63624233787687</v>
       </c>
       <c r="G15" t="n">
-        <v>100.7395358750273</v>
+        <v>74.73953587502734</v>
       </c>
       <c r="H15" t="n">
-        <v>107.1680871864211</v>
+        <v>81.16808718642113</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -1729,28 +1729,28 @@
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>322.2737972923793</v>
+        <v>296.2737972923793</v>
       </c>
       <c r="S15" t="n">
-        <v>241.5639999646113</v>
+        <v>215.5639999646113</v>
       </c>
       <c r="T15" t="n">
-        <v>180.3577652175138</v>
+        <v>154.3577652175138</v>
       </c>
       <c r="U15" t="n">
-        <v>175.2103597601867</v>
+        <v>149.2103597601867</v>
       </c>
       <c r="V15" t="n">
-        <v>189.5106671915202</v>
+        <v>163.5106671915202</v>
       </c>
       <c r="W15" t="n">
-        <v>207.3731429098285</v>
+        <v>181.3731429098285</v>
       </c>
       <c r="X15" t="n">
-        <v>194.8627394453875</v>
+        <v>168.8627394453875</v>
       </c>
       <c r="Y15" t="n">
-        <v>174.3913927661343</v>
+        <v>148.3913927661343</v>
       </c>
     </row>
     <row r="16">
@@ -1778,7 +1778,7 @@
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>3.77112610161862</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
@@ -1805,13 +1805,13 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>52.97841917455713</v>
       </c>
       <c r="R16" t="n">
-        <v>180.9596743555647</v>
+        <v>475.6021279811511</v>
       </c>
       <c r="S16" t="n">
-        <v>137.3734797028554</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
         <v>0</v>
@@ -1823,10 +1823,10 @@
         <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.372809838709685</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>22.44364543010755</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
         <v>0</v>
@@ -1839,28 +1839,28 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>256.9993129555745</v>
+        <v>230.9993129555745</v>
       </c>
       <c r="C17" t="n">
-        <v>224.4745782429939</v>
+        <v>198.4745782429939</v>
       </c>
       <c r="D17" t="n">
-        <v>185.3391557398498</v>
+        <v>159.3391557398498</v>
       </c>
       <c r="E17" t="n">
-        <v>179.3632896068686</v>
+        <v>153.3632896068686</v>
       </c>
       <c r="F17" t="n">
-        <v>179.8896287080119</v>
+        <v>153.8896287080119</v>
       </c>
       <c r="G17" t="n">
-        <v>178.7573722870162</v>
+        <v>152.7573722870162</v>
       </c>
       <c r="H17" t="n">
-        <v>183.0096587035274</v>
+        <v>157.0096587035274</v>
       </c>
       <c r="I17" t="n">
-        <v>5.493192557119869</v>
+        <v>3.410991385414028</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -1887,28 +1887,28 @@
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>25.87859882829446</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>269.8481678023229</v>
+        <v>243.8481678023229</v>
       </c>
       <c r="T17" t="n">
-        <v>361.6755817285639</v>
+        <v>335.6755817285639</v>
       </c>
       <c r="U17" t="n">
-        <v>424.2212965486107</v>
+        <v>398.2212965486107</v>
       </c>
       <c r="V17" t="n">
-        <v>404.8510241668239</v>
+        <v>378.8510241668239</v>
       </c>
       <c r="W17" t="n">
-        <v>413.3734759809475</v>
+        <v>387.3734759809475</v>
       </c>
       <c r="X17" t="n">
-        <v>367.2818334606677</v>
+        <v>341.2818334606677</v>
       </c>
       <c r="Y17" t="n">
-        <v>286.3174326828064</v>
+        <v>260.3174326828064</v>
       </c>
     </row>
     <row r="18">
@@ -1918,25 +1918,25 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>159.5565566463266</v>
+        <v>133.5565566463266</v>
       </c>
       <c r="C18" t="n">
-        <v>136.0999124455193</v>
+        <v>110.0999124455193</v>
       </c>
       <c r="D18" t="n">
-        <v>122.9376868977026</v>
+        <v>96.93768689770263</v>
       </c>
       <c r="E18" t="n">
-        <v>117.6720972219126</v>
+        <v>91.67209722191262</v>
       </c>
       <c r="F18" t="n">
-        <v>114.6362423378769</v>
+        <v>88.63624233787687</v>
       </c>
       <c r="G18" t="n">
-        <v>100.7395358750273</v>
+        <v>74.73953587502734</v>
       </c>
       <c r="H18" t="n">
-        <v>107.1680871864211</v>
+        <v>81.16808718642113</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
@@ -1966,28 +1966,28 @@
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>322.2737972923793</v>
+        <v>296.2737972923793</v>
       </c>
       <c r="S18" t="n">
-        <v>241.5639999646113</v>
+        <v>215.5639999646113</v>
       </c>
       <c r="T18" t="n">
-        <v>180.3577652175138</v>
+        <v>154.3577652175138</v>
       </c>
       <c r="U18" t="n">
-        <v>175.2103597601867</v>
+        <v>149.2103597601867</v>
       </c>
       <c r="V18" t="n">
-        <v>189.5106671915202</v>
+        <v>163.5106671915202</v>
       </c>
       <c r="W18" t="n">
-        <v>207.3731429098285</v>
+        <v>181.3731429098285</v>
       </c>
       <c r="X18" t="n">
-        <v>194.8627394453875</v>
+        <v>168.8627394453875</v>
       </c>
       <c r="Y18" t="n">
-        <v>174.3913927661343</v>
+        <v>148.3913927661343</v>
       </c>
     </row>
     <row r="19">
@@ -1997,25 +1997,25 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>62.11380033707866</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>47.72524664804467</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>60.53621805555548</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>55.98090483695654</v>
+        <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>49.38285596774193</v>
+        <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>20.04387284153003</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>3.77112610161862</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
@@ -2042,10 +2042,10 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>52.97841917455713</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>475.6021279811511</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -2060,13 +2060,13 @@
         <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.372809838709685</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>44.99390080162033</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2076,28 +2076,28 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>256.9993129555745</v>
+        <v>230.9993129555745</v>
       </c>
       <c r="C20" t="n">
-        <v>224.4745782429939</v>
+        <v>198.4745782429939</v>
       </c>
       <c r="D20" t="n">
-        <v>185.3391557398498</v>
+        <v>159.3391557398498</v>
       </c>
       <c r="E20" t="n">
-        <v>179.3632896068686</v>
+        <v>153.3632896068686</v>
       </c>
       <c r="F20" t="n">
-        <v>179.8896287080119</v>
+        <v>153.8896287080119</v>
       </c>
       <c r="G20" t="n">
-        <v>178.7573722870162</v>
+        <v>152.7573722870162</v>
       </c>
       <c r="H20" t="n">
-        <v>183.0096587035274</v>
+        <v>157.0096587035274</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>3.410991385414028</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2124,28 +2124,28 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>31.37179138541422</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>269.8481678023229</v>
+        <v>243.8481678023229</v>
       </c>
       <c r="T20" t="n">
-        <v>361.6755817285639</v>
+        <v>335.6755817285639</v>
       </c>
       <c r="U20" t="n">
-        <v>424.2212965486107</v>
+        <v>398.2212965486107</v>
       </c>
       <c r="V20" t="n">
-        <v>404.8510241668239</v>
+        <v>378.8510241668239</v>
       </c>
       <c r="W20" t="n">
-        <v>413.3734759809475</v>
+        <v>387.3734759809475</v>
       </c>
       <c r="X20" t="n">
-        <v>367.2818334606677</v>
+        <v>341.2818334606677</v>
       </c>
       <c r="Y20" t="n">
-        <v>286.3174326828064</v>
+        <v>260.3174326828064</v>
       </c>
     </row>
     <row r="21">
@@ -2155,25 +2155,25 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>159.5565566463266</v>
+        <v>133.5565566463266</v>
       </c>
       <c r="C21" t="n">
-        <v>136.0999124455193</v>
+        <v>110.0999124455193</v>
       </c>
       <c r="D21" t="n">
-        <v>122.9376868977026</v>
+        <v>96.93768689770263</v>
       </c>
       <c r="E21" t="n">
-        <v>117.6720972219126</v>
+        <v>91.67209722191262</v>
       </c>
       <c r="F21" t="n">
-        <v>114.6362423378769</v>
+        <v>88.63624233787687</v>
       </c>
       <c r="G21" t="n">
-        <v>100.7395358750273</v>
+        <v>74.73953587502734</v>
       </c>
       <c r="H21" t="n">
-        <v>107.1680871864211</v>
+        <v>81.16808718642113</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
@@ -2203,28 +2203,28 @@
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>322.2737972923793</v>
+        <v>296.2737972923793</v>
       </c>
       <c r="S21" t="n">
-        <v>241.5639999646113</v>
+        <v>215.5639999646113</v>
       </c>
       <c r="T21" t="n">
-        <v>180.3577652175138</v>
+        <v>154.3577652175138</v>
       </c>
       <c r="U21" t="n">
-        <v>175.2103597601867</v>
+        <v>149.2103597601867</v>
       </c>
       <c r="V21" t="n">
-        <v>189.5106671915202</v>
+        <v>163.5106671915202</v>
       </c>
       <c r="W21" t="n">
-        <v>207.3731429098285</v>
+        <v>181.3731429098285</v>
       </c>
       <c r="X21" t="n">
-        <v>194.8627394453875</v>
+        <v>168.8627394453875</v>
       </c>
       <c r="Y21" t="n">
-        <v>174.3913927661343</v>
+        <v>148.3913927661343</v>
       </c>
     </row>
     <row r="22">
@@ -2234,7 +2234,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>62.11380033707866</v>
+        <v>0</v>
       </c>
       <c r="C22" t="n">
         <v>0</v>
@@ -2252,7 +2252,7 @@
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>3.77112610161862</v>
+        <v>0</v>
       </c>
       <c r="I22" t="n">
         <v>0</v>
@@ -2276,16 +2276,16 @@
         <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>53.74128073011022</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>474.839266425598</v>
       </c>
       <c r="R22" t="n">
-        <v>56.38052116902366</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>137.3734797028554</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
         <v>0</v>
@@ -2297,13 +2297,13 @@
         <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.372809838709685</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>22.44364543010755</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>62.46535284946236</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -2313,28 +2313,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>262.4925055126944</v>
+        <v>230.9993129555745</v>
       </c>
       <c r="C23" t="n">
-        <v>224.4745782429939</v>
+        <v>198.4745782429939</v>
       </c>
       <c r="D23" t="n">
-        <v>185.3391557398498</v>
+        <v>159.3391557398498</v>
       </c>
       <c r="E23" t="n">
-        <v>179.3632896068686</v>
+        <v>153.3632896068686</v>
       </c>
       <c r="F23" t="n">
-        <v>179.8896287080119</v>
+        <v>153.8896287080119</v>
       </c>
       <c r="G23" t="n">
-        <v>178.7573722870162</v>
+        <v>152.7573722870162</v>
       </c>
       <c r="H23" t="n">
-        <v>183.0096587035274</v>
+        <v>157.0096587035274</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>3.410991385414028</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -2361,28 +2361,28 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>25.87859882829446</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>269.8481678023229</v>
+        <v>243.8481678023229</v>
       </c>
       <c r="T23" t="n">
-        <v>361.6755817285639</v>
+        <v>335.6755817285639</v>
       </c>
       <c r="U23" t="n">
-        <v>424.2212965486107</v>
+        <v>398.2212965486107</v>
       </c>
       <c r="V23" t="n">
-        <v>404.8510241668239</v>
+        <v>378.8510241668239</v>
       </c>
       <c r="W23" t="n">
-        <v>413.3734759809475</v>
+        <v>387.3734759809475</v>
       </c>
       <c r="X23" t="n">
-        <v>367.2818334606677</v>
+        <v>341.2818334606677</v>
       </c>
       <c r="Y23" t="n">
-        <v>286.3174326828064</v>
+        <v>260.3174326828064</v>
       </c>
     </row>
     <row r="24">
@@ -2392,25 +2392,25 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>159.5565566463266</v>
+        <v>133.5565566463266</v>
       </c>
       <c r="C24" t="n">
-        <v>136.0999124455193</v>
+        <v>110.0999124455193</v>
       </c>
       <c r="D24" t="n">
-        <v>122.9376868977026</v>
+        <v>96.93768689770263</v>
       </c>
       <c r="E24" t="n">
-        <v>117.6720972219126</v>
+        <v>91.67209722191262</v>
       </c>
       <c r="F24" t="n">
-        <v>114.6362423378769</v>
+        <v>88.63624233787687</v>
       </c>
       <c r="G24" t="n">
-        <v>100.7395358750273</v>
+        <v>74.73953587502734</v>
       </c>
       <c r="H24" t="n">
-        <v>107.1680871864211</v>
+        <v>81.16808718642113</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
@@ -2440,28 +2440,28 @@
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>322.2737972923793</v>
+        <v>296.2737972923793</v>
       </c>
       <c r="S24" t="n">
-        <v>241.5639999646113</v>
+        <v>215.5639999646113</v>
       </c>
       <c r="T24" t="n">
-        <v>180.3577652175138</v>
+        <v>154.3577652175138</v>
       </c>
       <c r="U24" t="n">
-        <v>175.2103597601867</v>
+        <v>149.2103597601867</v>
       </c>
       <c r="V24" t="n">
-        <v>189.5106671915202</v>
+        <v>163.5106671915202</v>
       </c>
       <c r="W24" t="n">
-        <v>207.3731429098285</v>
+        <v>181.3731429098285</v>
       </c>
       <c r="X24" t="n">
-        <v>194.8627394453875</v>
+        <v>168.8627394453875</v>
       </c>
       <c r="Y24" t="n">
-        <v>174.3913927661343</v>
+        <v>148.3913927661343</v>
       </c>
     </row>
     <row r="25">
@@ -2471,25 +2471,25 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>62.11380033707866</v>
+        <v>0</v>
       </c>
       <c r="C25" t="n">
-        <v>47.72524664804467</v>
+        <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>60.53621805555548</v>
+        <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>55.98090483695654</v>
+        <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>29.51163133132232</v>
+        <v>0</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>3.77112610161862</v>
+        <v>0</v>
       </c>
       <c r="I25" t="n">
         <v>0</v>
@@ -2516,10 +2516,10 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>52.97841917455713</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>475.6021279811511</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -2534,13 +2534,13 @@
         <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>1.372809838709685</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>22.44364543010755</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>62.46535284946236</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -2571,7 +2571,7 @@
         <v>183.0096587035274</v>
       </c>
       <c r="I26" t="n">
-        <v>5.493192557119869</v>
+        <v>0</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -2619,7 +2619,7 @@
         <v>367.2818334606677</v>
       </c>
       <c r="Y26" t="n">
-        <v>286.3174326828064</v>
+        <v>291.8106252399262</v>
       </c>
     </row>
     <row r="27">
@@ -2747,16 +2747,16 @@
         <v>0</v>
       </c>
       <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0</v>
+      </c>
+      <c r="R28" t="n">
         <v>340.7767994885277</v>
-      </c>
-      <c r="P28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>0</v>
-      </c>
-      <c r="R28" t="n">
-        <v>0</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -2790,7 +2790,7 @@
         <v>256.9993129555745</v>
       </c>
       <c r="C29" t="n">
-        <v>224.4745782429939</v>
+        <v>229.9677708001137</v>
       </c>
       <c r="D29" t="n">
         <v>185.3391557398498</v>
@@ -2835,7 +2835,7 @@
         <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>31.37179138541422</v>
+        <v>25.87859882829446</v>
       </c>
       <c r="S29" t="n">
         <v>269.8481678023229</v>
@@ -2987,13 +2987,13 @@
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>340.7767994885277</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>340.7767994885277</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -3045,7 +3045,7 @@
         <v>183.0096587035274</v>
       </c>
       <c r="I32" t="n">
-        <v>5.493192557119869</v>
+        <v>0</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -3084,7 +3084,7 @@
         <v>424.2212965486107</v>
       </c>
       <c r="V32" t="n">
-        <v>404.8510241668239</v>
+        <v>410.344216723944</v>
       </c>
       <c r="W32" t="n">
         <v>413.3734759809475</v>
@@ -3224,10 +3224,10 @@
         <v>0</v>
       </c>
       <c r="P34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" t="n">
         <v>340.7767994885277</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>0</v>
       </c>
       <c r="R34" t="n">
         <v>0</v>
@@ -3309,7 +3309,7 @@
         <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>3.965391385414537</v>
       </c>
       <c r="S35" t="n">
         <v>144.8481678023229</v>
@@ -3327,7 +3327,7 @@
         <v>288.3734759809475</v>
       </c>
       <c r="X35" t="n">
-        <v>246.2472248460823</v>
+        <v>242.2818334606677</v>
       </c>
       <c r="Y35" t="n">
         <v>161.3174326828064</v>
@@ -3340,10 +3340,10 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>97.23431917176916</v>
+        <v>34.55655664632661</v>
       </c>
       <c r="C36" t="n">
-        <v>361.0999124455193</v>
+        <v>11.09991244551929</v>
       </c>
       <c r="D36" t="n">
         <v>0</v>
@@ -3352,10 +3352,10 @@
         <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>73.04152018756567</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
@@ -3498,7 +3498,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>135.964704340989</v>
+        <v>131.9993129555745</v>
       </c>
       <c r="C38" t="n">
         <v>99.47457824299391</v>
@@ -3549,7 +3549,7 @@
         <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>144.8481678023229</v>
+        <v>148.8135591877373</v>
       </c>
       <c r="T38" t="n">
         <v>236.6755817285639</v>
@@ -3580,13 +3580,13 @@
         <v>34.55655664632661</v>
       </c>
       <c r="C39" t="n">
-        <v>11.09991244551929</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D39" t="n">
         <v>0</v>
       </c>
       <c r="E39" t="n">
-        <v>195.551376634094</v>
+        <v>0</v>
       </c>
       <c r="F39" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
         <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>217.1263858913485</v>
+        <v>0</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -3631,7 +3631,7 @@
         <v>116.5639999646113</v>
       </c>
       <c r="T39" t="n">
-        <v>55.35776521751382</v>
+        <v>118.0355277429563</v>
       </c>
       <c r="U39" t="n">
         <v>50.21035976018675</v>
@@ -3756,7 +3756,7 @@
         <v>58.00965870352741</v>
       </c>
       <c r="I41" t="n">
-        <v>3.965391385414508</v>
+        <v>0</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -3783,7 +3783,7 @@
         <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>3.965391385414537</v>
       </c>
       <c r="S41" t="n">
         <v>144.8481678023229</v>
@@ -3832,7 +3832,7 @@
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>0</v>
+        <v>332.1680871864211</v>
       </c>
       <c r="I42" t="n">
         <v>0</v>
@@ -3862,10 +3862,10 @@
         <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>547.2737972923793</v>
+        <v>277.7834726314007</v>
       </c>
       <c r="S42" t="n">
-        <v>179.2417624900537</v>
+        <v>116.5639999646113</v>
       </c>
       <c r="T42" t="n">
         <v>55.35776521751382</v>
@@ -3978,7 +3978,7 @@
         <v>99.47457824299391</v>
       </c>
       <c r="D44" t="n">
-        <v>60.33915573984979</v>
+        <v>64.30454712526431</v>
       </c>
       <c r="E44" t="n">
         <v>54.36328960686865</v>
@@ -4026,7 +4026,7 @@
         <v>144.8481678023229</v>
       </c>
       <c r="T44" t="n">
-        <v>240.6409731139784</v>
+        <v>236.6755817285639</v>
       </c>
       <c r="U44" t="n">
         <v>299.2212965486107</v>
@@ -4054,7 +4054,7 @@
         <v>34.55655664632661</v>
       </c>
       <c r="C45" t="n">
-        <v>73.77767497096173</v>
+        <v>11.09991244551929</v>
       </c>
       <c r="D45" t="n">
         <v>0</v>
@@ -4063,7 +4063,7 @@
         <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -4102,13 +4102,13 @@
         <v>197.2737972923793</v>
       </c>
       <c r="S45" t="n">
-        <v>466.5639999646113</v>
+        <v>116.5639999646113</v>
       </c>
       <c r="T45" t="n">
         <v>55.35776521751382</v>
       </c>
       <c r="U45" t="n">
-        <v>50.21035976018675</v>
+        <v>123.2518799477523</v>
       </c>
       <c r="V45" t="n">
         <v>64.51066719152016</v>
@@ -4297,25 +4297,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>112.4501851396645</v>
+        <v>141.4463380542246</v>
       </c>
       <c r="C2" t="n">
-        <v>62.47586368209485</v>
+        <v>91.47201659665494</v>
       </c>
       <c r="D2" t="n">
-        <v>52.03227202568092</v>
+        <v>81.02842494024101</v>
       </c>
       <c r="E2" t="n">
-        <v>47.62490878641967</v>
+        <v>76.62106170097975</v>
       </c>
       <c r="F2" t="n">
-        <v>42.68588988943799</v>
+        <v>71.68204280399807</v>
       </c>
       <c r="G2" t="n">
-        <v>38.89056434699738</v>
+        <v>67.88671726155745</v>
       </c>
       <c r="H2" t="n">
-        <v>30.8</v>
+        <v>59.79615291456007</v>
       </c>
       <c r="I2" t="n">
         <v>30.8</v>
@@ -4348,25 +4348,25 @@
         <v>1540</v>
       </c>
       <c r="S2" t="n">
-        <v>1415.197616982083</v>
+        <v>1444.193769896644</v>
       </c>
       <c r="T2" t="n">
-        <v>1226.636423316867</v>
+        <v>1255.632576231427</v>
       </c>
       <c r="U2" t="n">
-        <v>974.8977399344323</v>
+        <v>1003.893892848992</v>
       </c>
       <c r="V2" t="n">
-        <v>742.7249882507717</v>
+        <v>771.7211411653319</v>
       </c>
       <c r="W2" t="n">
-        <v>501.9436993811278</v>
+        <v>530.9398522956878</v>
       </c>
       <c r="X2" t="n">
-        <v>307.7196251784331</v>
+        <v>336.7157780929932</v>
       </c>
       <c r="Y2" t="n">
-        <v>195.2777739836791</v>
+        <v>224.2739268982392</v>
       </c>
     </row>
     <row r="3">
@@ -4376,25 +4376,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>722.3619790837812</v>
+        <v>508.5131152965754</v>
       </c>
       <c r="C3" t="n">
-        <v>579.1494159256323</v>
+        <v>508.5131152965754</v>
       </c>
       <c r="D3" t="n">
-        <v>579.1494159256323</v>
+        <v>508.5131152965754</v>
       </c>
       <c r="E3" t="n">
-        <v>579.1494159256323</v>
+        <v>508.5131152965754</v>
       </c>
       <c r="F3" t="n">
-        <v>579.1494159256323</v>
+        <v>366.3233203903244</v>
       </c>
       <c r="G3" t="n">
-        <v>250.1195817084329</v>
+        <v>366.3233203903244</v>
       </c>
       <c r="H3" t="n">
-        <v>250.1195817084329</v>
+        <v>30.8</v>
       </c>
       <c r="I3" t="n">
         <v>30.8</v>
@@ -4421,31 +4421,31 @@
         <v>1186.232420368536</v>
       </c>
       <c r="Q3" t="n">
-        <v>1011.404879873102</v>
+        <v>1186.232420368536</v>
       </c>
       <c r="R3" t="n">
-        <v>862.6434684666581</v>
+        <v>1037.471008962092</v>
       </c>
       <c r="S3" t="n">
-        <v>795.4071048660406</v>
+        <v>970.2346453614745</v>
       </c>
       <c r="T3" t="n">
-        <v>789.9952208079459</v>
+        <v>964.8227613033797</v>
       </c>
       <c r="U3" t="n">
-        <v>789.7827362016966</v>
+        <v>575.9338724144908</v>
       </c>
       <c r="V3" t="n">
-        <v>775.1254966143025</v>
+        <v>561.2766328270967</v>
       </c>
       <c r="W3" t="n">
-        <v>742.4253522609404</v>
+        <v>528.5764884737346</v>
       </c>
       <c r="X3" t="n">
-        <v>722.3619790837812</v>
+        <v>508.5131152965754</v>
       </c>
       <c r="Y3" t="n">
-        <v>722.3619790837812</v>
+        <v>508.5131152965754</v>
       </c>
     </row>
     <row r="4">
@@ -4455,16 +4455,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1022.260933153428</v>
+        <v>697.4052326007643</v>
       </c>
       <c r="C4" t="n">
-        <v>1148.262938971864</v>
+        <v>823.4072384192001</v>
       </c>
       <c r="D4" t="n">
-        <v>1178.916259347549</v>
+        <v>936.7263825442002</v>
       </c>
       <c r="E4" t="n">
-        <v>1178.916259347549</v>
+        <v>1054.555286755613</v>
       </c>
       <c r="F4" t="n">
         <v>1178.916259347549</v>
@@ -4485,22 +4485,22 @@
         <v>1540</v>
       </c>
       <c r="L4" t="n">
-        <v>1516.214517012344</v>
+        <v>1517.821760089168</v>
       </c>
       <c r="M4" t="n">
-        <v>1394.364404484516</v>
+        <v>1395.97164756134</v>
       </c>
       <c r="N4" t="n">
-        <v>1221.450187038369</v>
+        <v>1223.057430115194</v>
       </c>
       <c r="O4" t="n">
-        <v>978.5758798878493</v>
+        <v>980.1831229646734</v>
       </c>
       <c r="P4" t="n">
-        <v>688.2244684451448</v>
+        <v>689.8317115219688</v>
       </c>
       <c r="Q4" t="n">
-        <v>359.0938962980761</v>
+        <v>360.7011393749001</v>
       </c>
       <c r="R4" t="n">
         <v>30.8</v>
@@ -4509,22 +4509,22 @@
         <v>30.8</v>
       </c>
       <c r="T4" t="n">
-        <v>30.8</v>
+        <v>218.8756791588049</v>
       </c>
       <c r="U4" t="n">
-        <v>277.3511926382866</v>
+        <v>218.8756791588049</v>
       </c>
       <c r="V4" t="n">
-        <v>476.1725855242326</v>
+        <v>218.8756791588049</v>
       </c>
       <c r="W4" t="n">
-        <v>648.0635037839101</v>
+        <v>323.2078032312463</v>
       </c>
       <c r="X4" t="n">
-        <v>799.0942948081035</v>
+        <v>474.2385942554399</v>
       </c>
       <c r="Y4" t="n">
-        <v>910.5035954871358</v>
+        <v>585.6478949344721</v>
       </c>
     </row>
     <row r="5">
@@ -4534,22 +4534,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>141.4463380542246</v>
+        <v>112.4501851396645</v>
       </c>
       <c r="C5" t="n">
-        <v>91.47201659665494</v>
+        <v>62.47586368209485</v>
       </c>
       <c r="D5" t="n">
-        <v>81.02842494024101</v>
+        <v>52.03227202568092</v>
       </c>
       <c r="E5" t="n">
-        <v>76.62106170097975</v>
+        <v>47.62490878641967</v>
       </c>
       <c r="F5" t="n">
-        <v>71.68204280399807</v>
+        <v>42.68588988943799</v>
       </c>
       <c r="G5" t="n">
-        <v>67.88671726155745</v>
+        <v>38.89056434699738</v>
       </c>
       <c r="H5" t="n">
         <v>30.8</v>
@@ -4567,10 +4567,10 @@
         <v>777.6999999999999</v>
       </c>
       <c r="M5" t="n">
-        <v>777.6999999999999</v>
+        <v>1158.85</v>
       </c>
       <c r="N5" t="n">
-        <v>1158.85</v>
+        <v>1540</v>
       </c>
       <c r="O5" t="n">
         <v>1540</v>
@@ -4588,22 +4588,22 @@
         <v>1444.193769896644</v>
       </c>
       <c r="T5" t="n">
-        <v>1255.632576231427</v>
+        <v>1226.636423316867</v>
       </c>
       <c r="U5" t="n">
-        <v>1003.893892848992</v>
+        <v>974.8977399344323</v>
       </c>
       <c r="V5" t="n">
-        <v>771.7211411653319</v>
+        <v>742.7249882507717</v>
       </c>
       <c r="W5" t="n">
-        <v>530.9398522956878</v>
+        <v>501.9436993811278</v>
       </c>
       <c r="X5" t="n">
-        <v>336.7157780929932</v>
+        <v>307.7196251784331</v>
       </c>
       <c r="Y5" t="n">
-        <v>224.2739268982392</v>
+        <v>195.2777739836791</v>
       </c>
     </row>
     <row r="6">
@@ -4619,19 +4619,19 @@
         <v>897.189519579215</v>
       </c>
       <c r="D6" t="n">
-        <v>897.189519579215</v>
+        <v>702.8967456696003</v>
       </c>
       <c r="E6" t="n">
-        <v>897.189519579215</v>
+        <v>702.8967456696003</v>
       </c>
       <c r="F6" t="n">
-        <v>897.189519579215</v>
+        <v>359.8298342171994</v>
       </c>
       <c r="G6" t="n">
-        <v>585.6429020987573</v>
+        <v>30.8</v>
       </c>
       <c r="H6" t="n">
-        <v>250.1195817084329</v>
+        <v>30.8</v>
       </c>
       <c r="I6" t="n">
         <v>30.8</v>
@@ -4692,76 +4692,76 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1022.260933153428</v>
+        <v>701.4985197772105</v>
       </c>
       <c r="C7" t="n">
-        <v>1148.262938971864</v>
+        <v>701.4985197772105</v>
       </c>
       <c r="D7" t="n">
-        <v>1261.582083096864</v>
+        <v>701.4985197772105</v>
       </c>
       <c r="E7" t="n">
-        <v>1379.410987308277</v>
+        <v>761.2185634888302</v>
       </c>
       <c r="F7" t="n">
-        <v>1503.771959900212</v>
+        <v>885.5795360807657</v>
       </c>
       <c r="G7" t="n">
-        <v>1540</v>
+        <v>1038.986101967651</v>
       </c>
       <c r="H7" t="n">
-        <v>1540</v>
+        <v>1208.502687127049</v>
       </c>
       <c r="I7" t="n">
-        <v>1540</v>
+        <v>1429.635566063132</v>
       </c>
       <c r="J7" t="n">
-        <v>1540</v>
+        <v>1429.635566063132</v>
       </c>
       <c r="K7" t="n">
         <v>1540</v>
       </c>
       <c r="L7" t="n">
-        <v>1516.214517012344</v>
+        <v>1517.821760089168</v>
       </c>
       <c r="M7" t="n">
-        <v>1394.364404484516</v>
+        <v>1395.97164756134</v>
       </c>
       <c r="N7" t="n">
-        <v>1221.450187038369</v>
+        <v>1223.057430115194</v>
       </c>
       <c r="O7" t="n">
-        <v>978.5758798878493</v>
+        <v>980.1831229646734</v>
       </c>
       <c r="P7" t="n">
-        <v>688.2244684451448</v>
+        <v>689.8317115219688</v>
       </c>
       <c r="Q7" t="n">
-        <v>359.0938962980761</v>
+        <v>360.7011393749001</v>
       </c>
       <c r="R7" t="n">
         <v>30.8</v>
       </c>
       <c r="S7" t="n">
-        <v>30.8</v>
+        <v>68.05025509417312</v>
       </c>
       <c r="T7" t="n">
-        <v>30.8</v>
+        <v>256.125934252978</v>
       </c>
       <c r="U7" t="n">
-        <v>277.3511926382866</v>
+        <v>502.6771268912646</v>
       </c>
       <c r="V7" t="n">
-        <v>476.1725855242326</v>
+        <v>701.4985197772105</v>
       </c>
       <c r="W7" t="n">
-        <v>648.0635037839101</v>
+        <v>701.4985197772105</v>
       </c>
       <c r="X7" t="n">
-        <v>799.0942948081035</v>
+        <v>701.4985197772105</v>
       </c>
       <c r="Y7" t="n">
-        <v>910.5035954871358</v>
+        <v>701.4985197772105</v>
       </c>
     </row>
     <row r="8">
@@ -4801,13 +4801,13 @@
         <v>411.9499999999999</v>
       </c>
       <c r="L8" t="n">
-        <v>777.6999999999999</v>
+        <v>793.0999999999999</v>
       </c>
       <c r="M8" t="n">
         <v>1158.85</v>
       </c>
       <c r="N8" t="n">
-        <v>1540</v>
+        <v>1158.85</v>
       </c>
       <c r="O8" t="n">
         <v>1540</v>
@@ -4850,25 +4850,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>250.1195817084329</v>
+        <v>30.8</v>
       </c>
       <c r="C9" t="n">
-        <v>250.1195817084329</v>
+        <v>30.8</v>
       </c>
       <c r="D9" t="n">
-        <v>250.1195817084329</v>
+        <v>30.8</v>
       </c>
       <c r="E9" t="n">
-        <v>250.1195817084329</v>
+        <v>30.8</v>
       </c>
       <c r="F9" t="n">
-        <v>250.1195817084329</v>
+        <v>30.8</v>
       </c>
       <c r="G9" t="n">
-        <v>250.1195817084329</v>
+        <v>30.8</v>
       </c>
       <c r="H9" t="n">
-        <v>250.1195817084329</v>
+        <v>30.8</v>
       </c>
       <c r="I9" t="n">
         <v>30.8</v>
@@ -4898,28 +4898,28 @@
         <v>1186.232420368536</v>
       </c>
       <c r="R9" t="n">
-        <v>1037.471008962092</v>
+        <v>933.7541049937926</v>
       </c>
       <c r="S9" t="n">
-        <v>970.2346453614745</v>
+        <v>866.5177413931751</v>
       </c>
       <c r="T9" t="n">
-        <v>964.8227613033797</v>
+        <v>861.1058573350804</v>
       </c>
       <c r="U9" t="n">
-        <v>964.6102766971304</v>
+        <v>860.8933727288311</v>
       </c>
       <c r="V9" t="n">
-        <v>949.9530371097363</v>
+        <v>472.0044838399421</v>
       </c>
       <c r="W9" t="n">
-        <v>917.2528927563742</v>
+        <v>439.30433948658</v>
       </c>
       <c r="X9" t="n">
-        <v>897.189519579215</v>
+        <v>419.2409663094209</v>
       </c>
       <c r="Y9" t="n">
-        <v>638.5605480178538</v>
+        <v>419.2409663094209</v>
       </c>
     </row>
     <row r="10">
@@ -4959,46 +4959,46 @@
         <v>1540</v>
       </c>
       <c r="L10" t="n">
-        <v>1516.214517012344</v>
+        <v>1517.821760089168</v>
       </c>
       <c r="M10" t="n">
-        <v>1394.364404484516</v>
+        <v>1395.97164756134</v>
       </c>
       <c r="N10" t="n">
-        <v>1221.450187038369</v>
+        <v>1223.057430115194</v>
       </c>
       <c r="O10" t="n">
-        <v>978.5758798878493</v>
+        <v>980.1831229646734</v>
       </c>
       <c r="P10" t="n">
-        <v>688.2244684451448</v>
+        <v>689.8317115219688</v>
       </c>
       <c r="Q10" t="n">
-        <v>359.0938962980761</v>
+        <v>360.7011393749001</v>
       </c>
       <c r="R10" t="n">
         <v>30.8</v>
       </c>
       <c r="S10" t="n">
-        <v>42.98476868153026</v>
+        <v>30.8</v>
       </c>
       <c r="T10" t="n">
-        <v>42.98476868153026</v>
+        <v>30.8</v>
       </c>
       <c r="U10" t="n">
-        <v>42.98476868153026</v>
+        <v>30.8</v>
       </c>
       <c r="V10" t="n">
-        <v>42.98476868153026</v>
+        <v>30.8</v>
       </c>
       <c r="W10" t="n">
-        <v>42.98476868153026</v>
+        <v>30.8</v>
       </c>
       <c r="X10" t="n">
-        <v>42.98476868153026</v>
+        <v>30.8</v>
       </c>
       <c r="Y10" t="n">
-        <v>42.98476868153026</v>
+        <v>30.8</v>
       </c>
     </row>
     <row r="11">
@@ -5008,76 +5008,76 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1223.616245745725</v>
+        <v>1057.960488169967</v>
       </c>
       <c r="C11" t="n">
-        <v>996.8742475204788</v>
+        <v>857.4811162073474</v>
       </c>
       <c r="D11" t="n">
-        <v>809.6629790963881</v>
+        <v>696.532474045883</v>
       </c>
       <c r="E11" t="n">
-        <v>628.48793908945</v>
+        <v>541.6200603015712</v>
       </c>
       <c r="F11" t="n">
-        <v>446.7812434247916</v>
+        <v>386.175990899539</v>
       </c>
       <c r="G11" t="n">
-        <v>266.2182411146742</v>
+        <v>231.8756148520479</v>
       </c>
       <c r="H11" t="n">
-        <v>81.36</v>
+        <v>73.28</v>
       </c>
       <c r="I11" t="n">
-        <v>81.36</v>
+        <v>73.28</v>
       </c>
       <c r="J11" t="n">
-        <v>472.6691130376557</v>
+        <v>464.5891130376557</v>
       </c>
       <c r="K11" t="n">
-        <v>1182.375479385524</v>
+        <v>464.5891130376557</v>
       </c>
       <c r="L11" t="n">
-        <v>2089.404973955146</v>
+        <v>843.7526212654619</v>
       </c>
       <c r="M11" t="n">
-        <v>2600.253802684082</v>
+        <v>843.7526212654619</v>
       </c>
       <c r="N11" t="n">
-        <v>3114.957455978044</v>
+        <v>1456.972941040225</v>
       </c>
       <c r="O11" t="n">
-        <v>4068</v>
+        <v>2363.812941040225</v>
       </c>
       <c r="P11" t="n">
-        <v>4068</v>
+        <v>3225.400904947332</v>
       </c>
       <c r="Q11" t="n">
-        <v>4068</v>
+        <v>3664</v>
       </c>
       <c r="R11" t="n">
-        <v>4036.311321832915</v>
+        <v>3664</v>
       </c>
       <c r="S11" t="n">
-        <v>3763.737414961882</v>
+        <v>3417.688719391593</v>
       </c>
       <c r="T11" t="n">
-        <v>3398.408544528989</v>
+        <v>3078.622475221327</v>
       </c>
       <c r="U11" t="n">
-        <v>2969.902184378877</v>
+        <v>2676.378741333841</v>
       </c>
       <c r="V11" t="n">
-        <v>2560.961755927539</v>
+        <v>2293.70093914513</v>
       </c>
       <c r="W11" t="n">
-        <v>2143.412790290219</v>
+        <v>1898.969153926582</v>
       </c>
       <c r="X11" t="n">
-        <v>1772.421039319847</v>
+        <v>1554.240029218837</v>
       </c>
       <c r="Y11" t="n">
-        <v>1483.211511357417</v>
+        <v>1291.293127519033</v>
       </c>
     </row>
     <row r="12">
@@ -5087,76 +5087,76 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>787.6767292570302</v>
+        <v>622.0209716812727</v>
       </c>
       <c r="C12" t="n">
-        <v>650.2020702211521</v>
+        <v>510.8089389080209</v>
       </c>
       <c r="D12" t="n">
-        <v>526.022588506301</v>
+        <v>412.892083455796</v>
       </c>
       <c r="E12" t="n">
-        <v>407.1618842417428</v>
+        <v>320.294005453864</v>
       </c>
       <c r="F12" t="n">
-        <v>291.3677000620692</v>
+        <v>230.7624475368166</v>
       </c>
       <c r="G12" t="n">
-        <v>189.6105931175971</v>
+        <v>155.2679668549708</v>
       </c>
       <c r="H12" t="n">
-        <v>81.36</v>
+        <v>73.28</v>
       </c>
       <c r="I12" t="n">
-        <v>89.15487796756496</v>
+        <v>106.814877967565</v>
       </c>
       <c r="J12" t="n">
-        <v>435.8613981428639</v>
+        <v>479.2613981428639</v>
       </c>
       <c r="K12" t="n">
-        <v>847.8042142372474</v>
+        <v>916.9442142372473</v>
       </c>
       <c r="L12" t="n">
-        <v>1138.080378378698</v>
+        <v>1436.784675832447</v>
       </c>
       <c r="M12" t="n">
-        <v>1446.910920121557</v>
+        <v>1522.865217575307</v>
       </c>
       <c r="N12" t="n">
-        <v>1802.941204729126</v>
+        <v>1897.823338350157</v>
       </c>
       <c r="O12" t="n">
-        <v>2264.733656412845</v>
+        <v>2136.865790033876</v>
       </c>
       <c r="P12" t="n">
-        <v>2600.013000882351</v>
+        <v>2249.395134503382</v>
       </c>
       <c r="Q12" t="n">
-        <v>2651.414528442776</v>
+        <v>2249.395134503382</v>
       </c>
       <c r="R12" t="n">
-        <v>2325.885440268656</v>
+        <v>1950.128672591888</v>
       </c>
       <c r="S12" t="n">
-        <v>2081.881399900361</v>
+        <v>1732.38725848622</v>
       </c>
       <c r="T12" t="n">
-        <v>1899.70183907459</v>
+        <v>1576.470323923075</v>
       </c>
       <c r="U12" t="n">
-        <v>1722.721677700664</v>
+        <v>1425.752788811775</v>
       </c>
       <c r="V12" t="n">
-        <v>1531.296761345593</v>
+        <v>1260.59049871933</v>
       </c>
       <c r="W12" t="n">
-        <v>1321.828940224554</v>
+        <v>1077.385303860918</v>
       </c>
       <c r="X12" t="n">
-        <v>1124.997890279718</v>
+        <v>906.8168801787081</v>
       </c>
       <c r="Y12" t="n">
-        <v>948.8449682937237</v>
+        <v>756.92658445534</v>
       </c>
     </row>
     <row r="13">
@@ -5166,76 +5166,76 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>193.6715880782802</v>
+        <v>255.2662842199767</v>
       </c>
       <c r="C13" t="n">
-        <v>145.4642682317704</v>
+        <v>255.2662842199767</v>
       </c>
       <c r="D13" t="n">
-        <v>145.4642682317704</v>
+        <v>255.2662842199767</v>
       </c>
       <c r="E13" t="n">
-        <v>88.91789970959208</v>
+        <v>255.2662842199767</v>
       </c>
       <c r="F13" t="n">
-        <v>88.91789970959208</v>
+        <v>255.2662842199767</v>
       </c>
       <c r="G13" t="n">
-        <v>88.91789970959208</v>
+        <v>261.162850106862</v>
       </c>
       <c r="H13" t="n">
-        <v>85.10868142512882</v>
+        <v>283.1694352662595</v>
       </c>
       <c r="I13" t="n">
-        <v>132.9915603612117</v>
+        <v>356.7923142023425</v>
       </c>
       <c r="J13" t="n">
-        <v>320.8253010136631</v>
+        <v>570.3660548547938</v>
       </c>
       <c r="K13" t="n">
-        <v>320.8253010136631</v>
+        <v>570.3660548547938</v>
       </c>
       <c r="L13" t="n">
-        <v>320.8253010136631</v>
+        <v>396.0755213620876</v>
       </c>
       <c r="M13" t="n">
-        <v>81.36</v>
+        <v>123.7203583292089</v>
       </c>
       <c r="N13" t="n">
-        <v>81.36</v>
+        <v>123.7203583292089</v>
       </c>
       <c r="O13" t="n">
-        <v>81.36</v>
+        <v>123.7203583292089</v>
       </c>
       <c r="P13" t="n">
-        <v>81.36</v>
+        <v>123.7203583292089</v>
       </c>
       <c r="Q13" t="n">
-        <v>81.36</v>
+        <v>73.28</v>
       </c>
       <c r="R13" t="n">
-        <v>81.36</v>
+        <v>73.28</v>
       </c>
       <c r="S13" t="n">
-        <v>81.36</v>
+        <v>73.28</v>
       </c>
       <c r="T13" t="n">
-        <v>96.18567915880486</v>
+        <v>113.8456791588049</v>
       </c>
       <c r="U13" t="n">
-        <v>169.4868717970915</v>
+        <v>212.8868717970915</v>
       </c>
       <c r="V13" t="n">
-        <v>195.0582646830375</v>
+        <v>264.1982646830375</v>
       </c>
       <c r="W13" t="n">
-        <v>193.6715880782802</v>
+        <v>288.5791829427149</v>
       </c>
       <c r="X13" t="n">
-        <v>193.6715880782802</v>
+        <v>292.0999739669084</v>
       </c>
       <c r="Y13" t="n">
-        <v>193.6715880782802</v>
+        <v>255.2662842199767</v>
       </c>
     </row>
     <row r="14">
@@ -5245,76 +5245,76 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1223.616245745725</v>
+        <v>1057.960488169967</v>
       </c>
       <c r="C14" t="n">
-        <v>996.8742475204788</v>
+        <v>857.4811162073474</v>
       </c>
       <c r="D14" t="n">
-        <v>809.6629790963881</v>
+        <v>696.532474045883</v>
       </c>
       <c r="E14" t="n">
-        <v>628.48793908945</v>
+        <v>541.6200603015712</v>
       </c>
       <c r="F14" t="n">
-        <v>446.7812434247916</v>
+        <v>386.175990899539</v>
       </c>
       <c r="G14" t="n">
-        <v>266.2182411146742</v>
+        <v>231.8756148520479</v>
       </c>
       <c r="H14" t="n">
-        <v>81.36</v>
+        <v>73.28</v>
       </c>
       <c r="I14" t="n">
-        <v>81.36</v>
+        <v>73.28</v>
       </c>
       <c r="J14" t="n">
-        <v>472.6691130376557</v>
+        <v>73.28</v>
       </c>
       <c r="K14" t="n">
-        <v>1182.375479385524</v>
+        <v>73.28</v>
       </c>
       <c r="L14" t="n">
-        <v>2089.404973955146</v>
+        <v>332.9037925365269</v>
       </c>
       <c r="M14" t="n">
-        <v>2600.253802684082</v>
+        <v>843.7526212654619</v>
       </c>
       <c r="N14" t="n">
-        <v>3213.474122458845</v>
+        <v>1456.972941040225</v>
       </c>
       <c r="O14" t="n">
-        <v>3629.400904947332</v>
+        <v>2363.812941040225</v>
       </c>
       <c r="P14" t="n">
-        <v>3629.400904947332</v>
+        <v>3225.400904947332</v>
       </c>
       <c r="Q14" t="n">
-        <v>4068</v>
+        <v>3664</v>
       </c>
       <c r="R14" t="n">
-        <v>4036.311321832915</v>
+        <v>3660.554554156147</v>
       </c>
       <c r="S14" t="n">
-        <v>3763.737414961882</v>
+        <v>3414.243273547741</v>
       </c>
       <c r="T14" t="n">
-        <v>3398.408544528989</v>
+        <v>3075.177029377474</v>
       </c>
       <c r="U14" t="n">
-        <v>2969.902184378877</v>
+        <v>2672.933295489988</v>
       </c>
       <c r="V14" t="n">
-        <v>2560.961755927539</v>
+        <v>2290.255493301277</v>
       </c>
       <c r="W14" t="n">
-        <v>2143.412790290219</v>
+        <v>1898.969153926582</v>
       </c>
       <c r="X14" t="n">
-        <v>1772.421039319847</v>
+        <v>1554.240029218837</v>
       </c>
       <c r="Y14" t="n">
-        <v>1483.211511357417</v>
+        <v>1291.293127519033</v>
       </c>
     </row>
     <row r="15">
@@ -5324,76 +5324,76 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>787.6767292570302</v>
+        <v>622.0209716812727</v>
       </c>
       <c r="C15" t="n">
-        <v>650.2020702211521</v>
+        <v>510.8089389080209</v>
       </c>
       <c r="D15" t="n">
-        <v>526.022588506301</v>
+        <v>412.892083455796</v>
       </c>
       <c r="E15" t="n">
-        <v>407.1618842417428</v>
+        <v>320.294005453864</v>
       </c>
       <c r="F15" t="n">
-        <v>291.3677000620692</v>
+        <v>230.7624475368166</v>
       </c>
       <c r="G15" t="n">
-        <v>189.6105931175971</v>
+        <v>155.2679668549708</v>
       </c>
       <c r="H15" t="n">
-        <v>81.36</v>
+        <v>73.28</v>
       </c>
       <c r="I15" t="n">
-        <v>81.36</v>
+        <v>73.28</v>
       </c>
       <c r="J15" t="n">
-        <v>428.066520175299</v>
+        <v>197.2365201752989</v>
       </c>
       <c r="K15" t="n">
-        <v>643.9799167834981</v>
+        <v>634.9193362696824</v>
       </c>
       <c r="L15" t="n">
-        <v>1138.080378378698</v>
+        <v>1154.759797864883</v>
       </c>
       <c r="M15" t="n">
-        <v>1446.910920121557</v>
+        <v>1489.330339607742</v>
       </c>
       <c r="N15" t="n">
-        <v>1802.941204729126</v>
+        <v>1871.10062421531</v>
       </c>
       <c r="O15" t="n">
-        <v>2264.733656412845</v>
+        <v>2110.143075899029</v>
       </c>
       <c r="P15" t="n">
-        <v>2600.013000882351</v>
+        <v>2249.395134503382</v>
       </c>
       <c r="Q15" t="n">
-        <v>2651.414528442776</v>
+        <v>2249.395134503382</v>
       </c>
       <c r="R15" t="n">
-        <v>2325.885440268656</v>
+        <v>1950.128672591888</v>
       </c>
       <c r="S15" t="n">
-        <v>2081.881399900361</v>
+        <v>1732.38725848622</v>
       </c>
       <c r="T15" t="n">
-        <v>1899.70183907459</v>
+        <v>1576.470323923075</v>
       </c>
       <c r="U15" t="n">
-        <v>1722.721677700664</v>
+        <v>1425.752788811775</v>
       </c>
       <c r="V15" t="n">
-        <v>1531.296761345593</v>
+        <v>1260.59049871933</v>
       </c>
       <c r="W15" t="n">
-        <v>1321.828940224554</v>
+        <v>1077.385303860918</v>
       </c>
       <c r="X15" t="n">
-        <v>1124.997890279718</v>
+        <v>906.8168801787081</v>
       </c>
       <c r="Y15" t="n">
-        <v>948.8449682937237</v>
+        <v>756.92658445534</v>
       </c>
     </row>
     <row r="16">
@@ -5403,76 +5403,76 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>171.0012391589796</v>
+        <v>292.0999739669084</v>
       </c>
       <c r="C16" t="n">
-        <v>171.0012391589796</v>
+        <v>292.0999739669084</v>
       </c>
       <c r="D16" t="n">
-        <v>171.0012391589796</v>
+        <v>292.0999739669084</v>
       </c>
       <c r="E16" t="n">
-        <v>171.0012391589796</v>
+        <v>292.0999739669084</v>
       </c>
       <c r="F16" t="n">
-        <v>171.0012391589796</v>
+        <v>292.0999739669084</v>
       </c>
       <c r="G16" t="n">
-        <v>171.0012391589796</v>
+        <v>297.9965398537936</v>
       </c>
       <c r="H16" t="n">
-        <v>167.1920208745164</v>
+        <v>320.0031250131912</v>
       </c>
       <c r="I16" t="n">
-        <v>215.0748998105993</v>
+        <v>393.6260039492741</v>
       </c>
       <c r="J16" t="n">
-        <v>402.9086404630506</v>
+        <v>607.1997446017255</v>
       </c>
       <c r="K16" t="n">
-        <v>402.9086404630506</v>
+        <v>607.1997446017255</v>
       </c>
       <c r="L16" t="n">
-        <v>402.9086404630506</v>
+        <v>607.1997446017255</v>
       </c>
       <c r="M16" t="n">
-        <v>402.9086404630506</v>
+        <v>607.1997446017255</v>
       </c>
       <c r="N16" t="n">
-        <v>402.9086404630506</v>
+        <v>607.1997446017255</v>
       </c>
       <c r="O16" t="n">
-        <v>402.9086404630506</v>
+        <v>607.1997446017255</v>
       </c>
       <c r="P16" t="n">
-        <v>402.9086404630506</v>
+        <v>607.1997446017255</v>
       </c>
       <c r="Q16" t="n">
-        <v>402.9086404630506</v>
+        <v>553.6861898799506</v>
       </c>
       <c r="R16" t="n">
-        <v>220.1210906089449</v>
+        <v>73.28</v>
       </c>
       <c r="S16" t="n">
-        <v>81.36</v>
+        <v>73.28</v>
       </c>
       <c r="T16" t="n">
-        <v>96.18567915880486</v>
+        <v>113.8456791588049</v>
       </c>
       <c r="U16" t="n">
-        <v>169.4868717970915</v>
+        <v>212.8868717970915</v>
       </c>
       <c r="V16" t="n">
-        <v>195.0582646830375</v>
+        <v>264.1982646830375</v>
       </c>
       <c r="W16" t="n">
-        <v>193.6715880782802</v>
+        <v>288.5791829427149</v>
       </c>
       <c r="X16" t="n">
-        <v>171.0012391589796</v>
+        <v>292.0999739669084</v>
       </c>
       <c r="Y16" t="n">
-        <v>171.0012391589796</v>
+        <v>292.0999739669084</v>
       </c>
     </row>
     <row r="17">
@@ -5482,76 +5482,76 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1229.164925096351</v>
+        <v>1061.40593401382</v>
       </c>
       <c r="C17" t="n">
-        <v>1002.422926871105</v>
+        <v>860.9265620512</v>
       </c>
       <c r="D17" t="n">
-        <v>815.2116584470142</v>
+        <v>699.9779198897355</v>
       </c>
       <c r="E17" t="n">
-        <v>634.0366184400762</v>
+        <v>545.0655061454238</v>
       </c>
       <c r="F17" t="n">
-        <v>452.3299227754177</v>
+        <v>389.6214367433916</v>
       </c>
       <c r="G17" t="n">
-        <v>271.7669204653003</v>
+        <v>235.3210606959005</v>
       </c>
       <c r="H17" t="n">
-        <v>86.90867935062613</v>
+        <v>76.72544584385255</v>
       </c>
       <c r="I17" t="n">
-        <v>81.36</v>
+        <v>73.28</v>
       </c>
       <c r="J17" t="n">
-        <v>374.1524465568547</v>
+        <v>464.5891130376557</v>
       </c>
       <c r="K17" t="n">
-        <v>1083.858812904723</v>
+        <v>1174.295479385524</v>
       </c>
       <c r="L17" t="n">
-        <v>1990.888307474345</v>
+        <v>1750.592621265462</v>
       </c>
       <c r="M17" t="n">
-        <v>2501.73713620328</v>
+        <v>1750.592621265462</v>
       </c>
       <c r="N17" t="n">
-        <v>3114.957455978044</v>
+        <v>2363.812941040225</v>
       </c>
       <c r="O17" t="n">
-        <v>4068</v>
+        <v>2363.812941040225</v>
       </c>
       <c r="P17" t="n">
-        <v>4068</v>
+        <v>3225.400904947332</v>
       </c>
       <c r="Q17" t="n">
-        <v>4068</v>
+        <v>3664</v>
       </c>
       <c r="R17" t="n">
-        <v>4041.860001183541</v>
+        <v>3664</v>
       </c>
       <c r="S17" t="n">
-        <v>3769.286094312508</v>
+        <v>3417.688719391593</v>
       </c>
       <c r="T17" t="n">
-        <v>3403.957223879615</v>
+        <v>3078.622475221327</v>
       </c>
       <c r="U17" t="n">
-        <v>2975.450863729503</v>
+        <v>2676.378741333841</v>
       </c>
       <c r="V17" t="n">
-        <v>2566.510435278165</v>
+        <v>2293.70093914513</v>
       </c>
       <c r="W17" t="n">
-        <v>2148.961469640845</v>
+        <v>1902.414599770435</v>
       </c>
       <c r="X17" t="n">
-        <v>1777.969718670473</v>
+        <v>1557.68547506269</v>
       </c>
       <c r="Y17" t="n">
-        <v>1488.760190708043</v>
+        <v>1294.738573362885</v>
       </c>
     </row>
     <row r="18">
@@ -5561,76 +5561,76 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>787.6767292570302</v>
+        <v>622.0209716812727</v>
       </c>
       <c r="C18" t="n">
-        <v>650.2020702211521</v>
+        <v>510.8089389080209</v>
       </c>
       <c r="D18" t="n">
-        <v>526.022588506301</v>
+        <v>412.892083455796</v>
       </c>
       <c r="E18" t="n">
-        <v>407.1618842417428</v>
+        <v>320.294005453864</v>
       </c>
       <c r="F18" t="n">
-        <v>291.3677000620692</v>
+        <v>230.7624475368166</v>
       </c>
       <c r="G18" t="n">
-        <v>189.6105931175971</v>
+        <v>155.2679668549708</v>
       </c>
       <c r="H18" t="n">
-        <v>81.36</v>
+        <v>73.28</v>
       </c>
       <c r="I18" t="n">
-        <v>89.15487796756496</v>
+        <v>106.814877967565</v>
       </c>
       <c r="J18" t="n">
-        <v>435.8613981428639</v>
+        <v>479.2613981428639</v>
       </c>
       <c r="K18" t="n">
-        <v>847.8042142372474</v>
+        <v>916.9442142372473</v>
       </c>
       <c r="L18" t="n">
-        <v>1341.904675832448</v>
+        <v>1436.784675832447</v>
       </c>
       <c r="M18" t="n">
-        <v>1650.735217575307</v>
+        <v>1764.543053742589</v>
       </c>
       <c r="N18" t="n">
-        <v>2006.765502182875</v>
+        <v>1897.823338350157</v>
       </c>
       <c r="O18" t="n">
-        <v>2264.733656412845</v>
+        <v>2136.865790033876</v>
       </c>
       <c r="P18" t="n">
-        <v>2600.013000882351</v>
+        <v>2249.395134503382</v>
       </c>
       <c r="Q18" t="n">
-        <v>2651.414528442776</v>
+        <v>2249.395134503382</v>
       </c>
       <c r="R18" t="n">
-        <v>2325.885440268656</v>
+        <v>1950.128672591888</v>
       </c>
       <c r="S18" t="n">
-        <v>2081.881399900361</v>
+        <v>1732.38725848622</v>
       </c>
       <c r="T18" t="n">
-        <v>1899.70183907459</v>
+        <v>1576.470323923075</v>
       </c>
       <c r="U18" t="n">
-        <v>1722.721677700664</v>
+        <v>1425.752788811775</v>
       </c>
       <c r="V18" t="n">
-        <v>1531.296761345593</v>
+        <v>1260.59049871933</v>
       </c>
       <c r="W18" t="n">
-        <v>1321.828940224554</v>
+        <v>1077.385303860918</v>
       </c>
       <c r="X18" t="n">
-        <v>1124.997890279718</v>
+        <v>906.8168801787081</v>
       </c>
       <c r="Y18" t="n">
-        <v>948.8449682937237</v>
+        <v>756.92658445534</v>
       </c>
     </row>
     <row r="19">
@@ -5640,76 +5640,76 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>321.1986105570174</v>
+        <v>292.0999739669084</v>
       </c>
       <c r="C19" t="n">
-        <v>272.9912907105077</v>
+        <v>292.0999739669084</v>
       </c>
       <c r="D19" t="n">
-        <v>211.8435957048961</v>
+        <v>292.0999739669084</v>
       </c>
       <c r="E19" t="n">
-        <v>155.2972271827178</v>
+        <v>292.0999739669084</v>
       </c>
       <c r="F19" t="n">
-        <v>105.4155544880289</v>
+        <v>292.0999739669084</v>
       </c>
       <c r="G19" t="n">
-        <v>85.16921828446326</v>
+        <v>297.9965398537936</v>
       </c>
       <c r="H19" t="n">
-        <v>81.36</v>
+        <v>320.0031250131912</v>
       </c>
       <c r="I19" t="n">
-        <v>129.2428789360829</v>
+        <v>393.6260039492741</v>
       </c>
       <c r="J19" t="n">
-        <v>317.0766195885342</v>
+        <v>607.1997446017255</v>
       </c>
       <c r="K19" t="n">
-        <v>317.0766195885342</v>
+        <v>607.1997446017255</v>
       </c>
       <c r="L19" t="n">
-        <v>317.0766195885342</v>
+        <v>607.1997446017255</v>
       </c>
       <c r="M19" t="n">
-        <v>317.0766195885342</v>
+        <v>607.1997446017255</v>
       </c>
       <c r="N19" t="n">
-        <v>317.0766195885342</v>
+        <v>607.1997446017255</v>
       </c>
       <c r="O19" t="n">
-        <v>317.0766195885342</v>
+        <v>607.1997446017255</v>
       </c>
       <c r="P19" t="n">
-        <v>317.0766195885342</v>
+        <v>607.1997446017255</v>
       </c>
       <c r="Q19" t="n">
-        <v>317.0766195885342</v>
+        <v>553.6861898799506</v>
       </c>
       <c r="R19" t="n">
-        <v>317.0766195885342</v>
+        <v>73.28</v>
       </c>
       <c r="S19" t="n">
-        <v>317.0766195885342</v>
+        <v>73.28</v>
       </c>
       <c r="T19" t="n">
-        <v>331.9022987473391</v>
+        <v>113.8456791588049</v>
       </c>
       <c r="U19" t="n">
-        <v>405.2034913856257</v>
+        <v>212.8868717970915</v>
       </c>
       <c r="V19" t="n">
-        <v>430.7748842715717</v>
+        <v>264.1982646830375</v>
       </c>
       <c r="W19" t="n">
-        <v>429.3882076668144</v>
+        <v>288.5791829427149</v>
       </c>
       <c r="X19" t="n">
-        <v>429.3882076668144</v>
+        <v>292.0999739669084</v>
       </c>
       <c r="Y19" t="n">
-        <v>383.9398230187131</v>
+        <v>292.0999739669084</v>
       </c>
     </row>
     <row r="20">
@@ -5719,76 +5719,76 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1223.616245745725</v>
+        <v>1061.40593401382</v>
       </c>
       <c r="C20" t="n">
-        <v>996.8742475204788</v>
+        <v>860.9265620512</v>
       </c>
       <c r="D20" t="n">
-        <v>809.6629790963881</v>
+        <v>699.9779198897355</v>
       </c>
       <c r="E20" t="n">
-        <v>628.48793908945</v>
+        <v>545.0655061454238</v>
       </c>
       <c r="F20" t="n">
-        <v>446.7812434247916</v>
+        <v>389.6214367433916</v>
       </c>
       <c r="G20" t="n">
-        <v>266.2182411146742</v>
+        <v>235.3210606959005</v>
       </c>
       <c r="H20" t="n">
-        <v>81.36</v>
+        <v>76.72544584385255</v>
       </c>
       <c r="I20" t="n">
-        <v>81.36</v>
+        <v>73.28</v>
       </c>
       <c r="J20" t="n">
-        <v>472.6691130376557</v>
+        <v>464.5891130376557</v>
       </c>
       <c r="K20" t="n">
-        <v>472.6691130376557</v>
+        <v>1174.295479385524</v>
       </c>
       <c r="L20" t="n">
-        <v>690.7012485145707</v>
+        <v>1239.743792536527</v>
       </c>
       <c r="M20" t="n">
-        <v>1201.550077243506</v>
+        <v>1750.592621265462</v>
       </c>
       <c r="N20" t="n">
-        <v>1814.770397018269</v>
+        <v>2363.812941040225</v>
       </c>
       <c r="O20" t="n">
-        <v>2767.812941040225</v>
+        <v>2363.812941040225</v>
       </c>
       <c r="P20" t="n">
-        <v>3629.400904947332</v>
+        <v>3225.400904947332</v>
       </c>
       <c r="Q20" t="n">
-        <v>4068</v>
+        <v>3664</v>
       </c>
       <c r="R20" t="n">
-        <v>4036.311321832915</v>
+        <v>3664</v>
       </c>
       <c r="S20" t="n">
-        <v>3763.737414961882</v>
+        <v>3417.688719391593</v>
       </c>
       <c r="T20" t="n">
-        <v>3398.408544528989</v>
+        <v>3078.622475221327</v>
       </c>
       <c r="U20" t="n">
-        <v>2969.902184378877</v>
+        <v>2676.378741333841</v>
       </c>
       <c r="V20" t="n">
-        <v>2560.961755927539</v>
+        <v>2293.70093914513</v>
       </c>
       <c r="W20" t="n">
-        <v>2143.412790290219</v>
+        <v>1902.414599770435</v>
       </c>
       <c r="X20" t="n">
-        <v>1772.421039319847</v>
+        <v>1557.68547506269</v>
       </c>
       <c r="Y20" t="n">
-        <v>1483.211511357417</v>
+        <v>1294.738573362885</v>
       </c>
     </row>
     <row r="21">
@@ -5798,76 +5798,76 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>787.6767292570302</v>
+        <v>622.0209716812727</v>
       </c>
       <c r="C21" t="n">
-        <v>650.2020702211521</v>
+        <v>510.8089389080209</v>
       </c>
       <c r="D21" t="n">
-        <v>526.022588506301</v>
+        <v>412.892083455796</v>
       </c>
       <c r="E21" t="n">
-        <v>407.1618842417428</v>
+        <v>320.294005453864</v>
       </c>
       <c r="F21" t="n">
-        <v>291.3677000620692</v>
+        <v>230.7624475368166</v>
       </c>
       <c r="G21" t="n">
-        <v>189.6105931175971</v>
+        <v>155.2679668549708</v>
       </c>
       <c r="H21" t="n">
-        <v>81.36</v>
+        <v>73.28</v>
       </c>
       <c r="I21" t="n">
-        <v>81.36</v>
+        <v>106.814877967565</v>
       </c>
       <c r="J21" t="n">
-        <v>428.066520175299</v>
+        <v>479.2613981428639</v>
       </c>
       <c r="K21" t="n">
-        <v>840.0093362696824</v>
+        <v>916.9442142372473</v>
       </c>
       <c r="L21" t="n">
-        <v>1334.109797864882</v>
+        <v>1436.784675832447</v>
       </c>
       <c r="M21" t="n">
-        <v>1446.910920121557</v>
+        <v>1764.543053742589</v>
       </c>
       <c r="N21" t="n">
-        <v>1802.941204729126</v>
+        <v>1897.823338350157</v>
       </c>
       <c r="O21" t="n">
-        <v>2264.733656412845</v>
+        <v>2136.865790033876</v>
       </c>
       <c r="P21" t="n">
-        <v>2600.013000882351</v>
+        <v>2249.395134503382</v>
       </c>
       <c r="Q21" t="n">
-        <v>2651.414528442776</v>
+        <v>2249.395134503382</v>
       </c>
       <c r="R21" t="n">
-        <v>2325.885440268656</v>
+        <v>1950.128672591888</v>
       </c>
       <c r="S21" t="n">
-        <v>2081.881399900361</v>
+        <v>1732.38725848622</v>
       </c>
       <c r="T21" t="n">
-        <v>1899.70183907459</v>
+        <v>1576.470323923075</v>
       </c>
       <c r="U21" t="n">
-        <v>1722.721677700664</v>
+        <v>1425.752788811775</v>
       </c>
       <c r="V21" t="n">
-        <v>1531.296761345593</v>
+        <v>1260.59049871933</v>
       </c>
       <c r="W21" t="n">
-        <v>1321.828940224554</v>
+        <v>1077.385303860918</v>
       </c>
       <c r="X21" t="n">
-        <v>1124.997890279718</v>
+        <v>906.8168801787081</v>
       </c>
       <c r="Y21" t="n">
-        <v>948.8449682937237</v>
+        <v>756.92658445534</v>
       </c>
     </row>
     <row r="22">
@@ -5877,76 +5877,76 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>85.16921828446326</v>
+        <v>292.0999739669084</v>
       </c>
       <c r="C22" t="n">
-        <v>85.16921828446326</v>
+        <v>292.0999739669084</v>
       </c>
       <c r="D22" t="n">
-        <v>85.16921828446326</v>
+        <v>292.0999739669084</v>
       </c>
       <c r="E22" t="n">
-        <v>85.16921828446326</v>
+        <v>292.0999739669084</v>
       </c>
       <c r="F22" t="n">
-        <v>85.16921828446326</v>
+        <v>292.0999739669084</v>
       </c>
       <c r="G22" t="n">
-        <v>85.16921828446326</v>
+        <v>297.9965398537936</v>
       </c>
       <c r="H22" t="n">
-        <v>81.36</v>
+        <v>320.0031250131912</v>
       </c>
       <c r="I22" t="n">
-        <v>129.2428789360829</v>
+        <v>393.6260039492741</v>
       </c>
       <c r="J22" t="n">
-        <v>317.0766195885342</v>
+        <v>607.1997446017255</v>
       </c>
       <c r="K22" t="n">
-        <v>317.0766195885342</v>
+        <v>607.1997446017255</v>
       </c>
       <c r="L22" t="n">
-        <v>317.0766195885342</v>
+        <v>607.1997446017255</v>
       </c>
       <c r="M22" t="n">
-        <v>317.0766195885342</v>
+        <v>607.1997446017255</v>
       </c>
       <c r="N22" t="n">
-        <v>317.0766195885342</v>
+        <v>607.1997446017255</v>
       </c>
       <c r="O22" t="n">
-        <v>317.0766195885342</v>
+        <v>607.1997446017255</v>
       </c>
       <c r="P22" t="n">
-        <v>317.0766195885342</v>
+        <v>552.9156226521192</v>
       </c>
       <c r="Q22" t="n">
-        <v>317.0766195885342</v>
+        <v>73.28</v>
       </c>
       <c r="R22" t="n">
-        <v>260.1265982056821</v>
+        <v>73.28</v>
       </c>
       <c r="S22" t="n">
-        <v>121.3655075967372</v>
+        <v>73.28</v>
       </c>
       <c r="T22" t="n">
-        <v>136.191186755542</v>
+        <v>113.8456791588049</v>
       </c>
       <c r="U22" t="n">
-        <v>209.4923793938287</v>
+        <v>212.8868717970915</v>
       </c>
       <c r="V22" t="n">
-        <v>235.0637722797746</v>
+        <v>264.1982646830375</v>
       </c>
       <c r="W22" t="n">
-        <v>233.6770956750174</v>
+        <v>288.5791829427149</v>
       </c>
       <c r="X22" t="n">
-        <v>211.0067467557168</v>
+        <v>292.0999739669084</v>
       </c>
       <c r="Y22" t="n">
-        <v>147.9104307461589</v>
+        <v>292.0999739669084</v>
       </c>
     </row>
     <row r="23">
@@ -5956,76 +5956,76 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1223.616245745725</v>
+        <v>1061.40593401382</v>
       </c>
       <c r="C23" t="n">
-        <v>996.8742475204788</v>
+        <v>860.9265620512</v>
       </c>
       <c r="D23" t="n">
-        <v>809.6629790963881</v>
+        <v>699.9779198897355</v>
       </c>
       <c r="E23" t="n">
-        <v>628.48793908945</v>
+        <v>545.0655061454238</v>
       </c>
       <c r="F23" t="n">
-        <v>446.7812434247916</v>
+        <v>389.6214367433916</v>
       </c>
       <c r="G23" t="n">
-        <v>266.2182411146742</v>
+        <v>235.3210606959005</v>
       </c>
       <c r="H23" t="n">
-        <v>81.36</v>
+        <v>76.72544584385255</v>
       </c>
       <c r="I23" t="n">
-        <v>81.36</v>
+        <v>73.28</v>
       </c>
       <c r="J23" t="n">
-        <v>472.6691130376557</v>
+        <v>464.5891130376557</v>
       </c>
       <c r="K23" t="n">
-        <v>1182.375479385524</v>
+        <v>464.5891130376557</v>
       </c>
       <c r="L23" t="n">
-        <v>2089.404973955146</v>
+        <v>771.5028875891945</v>
       </c>
       <c r="M23" t="n">
-        <v>2600.253802684082</v>
+        <v>1282.35171631813</v>
       </c>
       <c r="N23" t="n">
-        <v>3213.474122458845</v>
+        <v>1895.572036092893</v>
       </c>
       <c r="O23" t="n">
-        <v>3629.400904947332</v>
+        <v>2802.412036092893</v>
       </c>
       <c r="P23" t="n">
-        <v>3629.400904947332</v>
+        <v>3664</v>
       </c>
       <c r="Q23" t="n">
-        <v>4068</v>
+        <v>3664</v>
       </c>
       <c r="R23" t="n">
-        <v>4041.860001183541</v>
+        <v>3664</v>
       </c>
       <c r="S23" t="n">
-        <v>3769.286094312508</v>
+        <v>3417.688719391593</v>
       </c>
       <c r="T23" t="n">
-        <v>3403.957223879615</v>
+        <v>3078.622475221327</v>
       </c>
       <c r="U23" t="n">
-        <v>2975.450863729503</v>
+        <v>2676.378741333841</v>
       </c>
       <c r="V23" t="n">
-        <v>2566.510435278165</v>
+        <v>2293.70093914513</v>
       </c>
       <c r="W23" t="n">
-        <v>2148.961469640845</v>
+        <v>1902.414599770435</v>
       </c>
       <c r="X23" t="n">
-        <v>1777.969718670473</v>
+        <v>1557.68547506269</v>
       </c>
       <c r="Y23" t="n">
-        <v>1488.760190708043</v>
+        <v>1294.738573362885</v>
       </c>
     </row>
     <row r="24">
@@ -6035,76 +6035,76 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>787.6767292570302</v>
+        <v>622.0209716812727</v>
       </c>
       <c r="C24" t="n">
-        <v>650.2020702211521</v>
+        <v>510.8089389080209</v>
       </c>
       <c r="D24" t="n">
-        <v>526.022588506301</v>
+        <v>412.892083455796</v>
       </c>
       <c r="E24" t="n">
-        <v>407.1618842417428</v>
+        <v>320.294005453864</v>
       </c>
       <c r="F24" t="n">
-        <v>291.3677000620692</v>
+        <v>230.7624475368166</v>
       </c>
       <c r="G24" t="n">
-        <v>189.6105931175971</v>
+        <v>155.2679668549708</v>
       </c>
       <c r="H24" t="n">
-        <v>81.36</v>
+        <v>73.28</v>
       </c>
       <c r="I24" t="n">
-        <v>81.36</v>
+        <v>106.814877967565</v>
       </c>
       <c r="J24" t="n">
-        <v>428.066520175299</v>
+        <v>230.7713981428639</v>
       </c>
       <c r="K24" t="n">
-        <v>695.3814443439232</v>
+        <v>668.4542142372472</v>
       </c>
       <c r="L24" t="n">
-        <v>1189.481905939123</v>
+        <v>1188.294675832447</v>
       </c>
       <c r="M24" t="n">
-        <v>1498.312447681983</v>
+        <v>1274.375217575307</v>
       </c>
       <c r="N24" t="n">
-        <v>1854.342732289551</v>
+        <v>1407.655502182875</v>
       </c>
       <c r="O24" t="n">
-        <v>2316.13518397327</v>
+        <v>1811.23426247345</v>
       </c>
       <c r="P24" t="n">
-        <v>2651.414528442776</v>
+        <v>2172.253606942957</v>
       </c>
       <c r="Q24" t="n">
-        <v>2651.414528442776</v>
+        <v>2249.395134503382</v>
       </c>
       <c r="R24" t="n">
-        <v>2325.885440268656</v>
+        <v>1950.128672591888</v>
       </c>
       <c r="S24" t="n">
-        <v>2081.881399900361</v>
+        <v>1732.38725848622</v>
       </c>
       <c r="T24" t="n">
-        <v>1899.70183907459</v>
+        <v>1576.470323923075</v>
       </c>
       <c r="U24" t="n">
-        <v>1722.721677700664</v>
+        <v>1425.752788811775</v>
       </c>
       <c r="V24" t="n">
-        <v>1531.296761345593</v>
+        <v>1260.59049871933</v>
       </c>
       <c r="W24" t="n">
-        <v>1321.828940224554</v>
+        <v>1077.385303860918</v>
       </c>
       <c r="X24" t="n">
-        <v>1124.997890279718</v>
+        <v>906.8168801787081</v>
       </c>
       <c r="Y24" t="n">
-        <v>948.8449682937237</v>
+        <v>756.92658445534</v>
       </c>
     </row>
     <row r="25">
@@ -6114,76 +6114,76 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>280.8803302762603</v>
+        <v>292.0999739669084</v>
       </c>
       <c r="C25" t="n">
-        <v>232.6730104297505</v>
+        <v>292.0999739669084</v>
       </c>
       <c r="D25" t="n">
-        <v>171.5253154241389</v>
+        <v>292.0999739669084</v>
       </c>
       <c r="E25" t="n">
-        <v>114.9789469019606</v>
+        <v>292.0999739669084</v>
       </c>
       <c r="F25" t="n">
-        <v>85.16921828446326</v>
+        <v>292.0999739669084</v>
       </c>
       <c r="G25" t="n">
-        <v>85.16921828446326</v>
+        <v>297.9965398537936</v>
       </c>
       <c r="H25" t="n">
-        <v>81.36</v>
+        <v>320.0031250131912</v>
       </c>
       <c r="I25" t="n">
-        <v>129.2428789360829</v>
+        <v>393.6260039492741</v>
       </c>
       <c r="J25" t="n">
-        <v>317.0766195885342</v>
+        <v>607.1997446017255</v>
       </c>
       <c r="K25" t="n">
-        <v>317.0766195885342</v>
+        <v>607.1997446017255</v>
       </c>
       <c r="L25" t="n">
-        <v>317.0766195885342</v>
+        <v>607.1997446017255</v>
       </c>
       <c r="M25" t="n">
-        <v>317.0766195885342</v>
+        <v>607.1997446017255</v>
       </c>
       <c r="N25" t="n">
-        <v>317.0766195885342</v>
+        <v>607.1997446017255</v>
       </c>
       <c r="O25" t="n">
-        <v>317.0766195885342</v>
+        <v>607.1997446017255</v>
       </c>
       <c r="P25" t="n">
-        <v>317.0766195885342</v>
+        <v>607.1997446017255</v>
       </c>
       <c r="Q25" t="n">
-        <v>317.0766195885342</v>
+        <v>553.6861898799506</v>
       </c>
       <c r="R25" t="n">
-        <v>317.0766195885342</v>
+        <v>73.28</v>
       </c>
       <c r="S25" t="n">
-        <v>317.0766195885342</v>
+        <v>73.28</v>
       </c>
       <c r="T25" t="n">
-        <v>331.9022987473391</v>
+        <v>113.8456791588049</v>
       </c>
       <c r="U25" t="n">
-        <v>405.2034913856257</v>
+        <v>212.8868717970915</v>
       </c>
       <c r="V25" t="n">
-        <v>430.7748842715717</v>
+        <v>264.1982646830375</v>
       </c>
       <c r="W25" t="n">
-        <v>429.3882076668144</v>
+        <v>288.5791829427149</v>
       </c>
       <c r="X25" t="n">
-        <v>406.7178587475138</v>
+        <v>292.0999739669084</v>
       </c>
       <c r="Y25" t="n">
-        <v>343.6215427379559</v>
+        <v>292.0999739669084</v>
       </c>
     </row>
     <row r="26">
@@ -6193,25 +6193,25 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1229.164925096351</v>
+        <v>1223.616245745725</v>
       </c>
       <c r="C26" t="n">
-        <v>1002.422926871105</v>
+        <v>996.8742475204788</v>
       </c>
       <c r="D26" t="n">
-        <v>815.2116584470142</v>
+        <v>809.6629790963881</v>
       </c>
       <c r="E26" t="n">
-        <v>634.0366184400762</v>
+        <v>628.48793908945</v>
       </c>
       <c r="F26" t="n">
-        <v>452.3299227754177</v>
+        <v>446.7812434247916</v>
       </c>
       <c r="G26" t="n">
-        <v>271.7669204653003</v>
+        <v>266.2182411146742</v>
       </c>
       <c r="H26" t="n">
-        <v>86.90867935062613</v>
+        <v>81.36</v>
       </c>
       <c r="I26" t="n">
         <v>81.36</v>
@@ -6223,16 +6223,16 @@
         <v>1182.375479385524</v>
       </c>
       <c r="L26" t="n">
-        <v>1643.743792536527</v>
+        <v>2089.404973955146</v>
       </c>
       <c r="M26" t="n">
-        <v>2154.592621265462</v>
+        <v>2600.253802684082</v>
       </c>
       <c r="N26" t="n">
-        <v>2767.812941040225</v>
+        <v>3213.474122458845</v>
       </c>
       <c r="O26" t="n">
-        <v>2767.812941040225</v>
+        <v>3629.400904947332</v>
       </c>
       <c r="P26" t="n">
         <v>3629.400904947332</v>
@@ -6262,7 +6262,7 @@
         <v>1777.969718670473</v>
       </c>
       <c r="Y26" t="n">
-        <v>1488.760190708043</v>
+        <v>1483.211511357417</v>
       </c>
     </row>
     <row r="27">
@@ -6293,19 +6293,19 @@
         <v>81.36</v>
       </c>
       <c r="I27" t="n">
-        <v>81.36</v>
+        <v>89.15487796756496</v>
       </c>
       <c r="J27" t="n">
-        <v>428.066520175299</v>
+        <v>232.0371006891147</v>
       </c>
       <c r="K27" t="n">
-        <v>840.0093362696824</v>
+        <v>643.9799167834981</v>
       </c>
       <c r="L27" t="n">
-        <v>1334.109797864882</v>
+        <v>1138.080378378698</v>
       </c>
       <c r="M27" t="n">
-        <v>1642.940339607742</v>
+        <v>1446.910920121557</v>
       </c>
       <c r="N27" t="n">
         <v>1802.941204729126</v>
@@ -6390,13 +6390,13 @@
         <v>425.5789893823512</v>
       </c>
       <c r="O28" t="n">
-        <v>81.36</v>
+        <v>425.5789893823512</v>
       </c>
       <c r="P28" t="n">
-        <v>81.36</v>
+        <v>425.5789893823512</v>
       </c>
       <c r="Q28" t="n">
-        <v>81.36</v>
+        <v>425.5789893823512</v>
       </c>
       <c r="R28" t="n">
         <v>81.36</v>
@@ -6430,7 +6430,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1223.616245745725</v>
+        <v>1229.164925096351</v>
       </c>
       <c r="C29" t="n">
         <v>996.8742475204788</v>
@@ -6454,22 +6454,22 @@
         <v>81.36</v>
       </c>
       <c r="J29" t="n">
-        <v>472.6691130376557</v>
+        <v>81.36</v>
       </c>
       <c r="K29" t="n">
-        <v>1182.375479385524</v>
+        <v>791.0663663478683</v>
       </c>
       <c r="L29" t="n">
-        <v>2089.404973955146</v>
+        <v>1643.743792536527</v>
       </c>
       <c r="M29" t="n">
-        <v>2089.404973955146</v>
+        <v>2154.592621265462</v>
       </c>
       <c r="N29" t="n">
-        <v>2702.62529372991</v>
+        <v>2767.812941040225</v>
       </c>
       <c r="O29" t="n">
-        <v>3629.400904947332</v>
+        <v>2767.812941040225</v>
       </c>
       <c r="P29" t="n">
         <v>3629.400904947332</v>
@@ -6478,28 +6478,28 @@
         <v>4068</v>
       </c>
       <c r="R29" t="n">
-        <v>4036.311321832915</v>
+        <v>4041.860001183541</v>
       </c>
       <c r="S29" t="n">
-        <v>3763.737414961882</v>
+        <v>3769.286094312508</v>
       </c>
       <c r="T29" t="n">
-        <v>3398.408544528989</v>
+        <v>3403.957223879615</v>
       </c>
       <c r="U29" t="n">
-        <v>2969.902184378877</v>
+        <v>2975.450863729503</v>
       </c>
       <c r="V29" t="n">
-        <v>2560.961755927539</v>
+        <v>2566.510435278165</v>
       </c>
       <c r="W29" t="n">
-        <v>2143.412790290219</v>
+        <v>2148.961469640845</v>
       </c>
       <c r="X29" t="n">
-        <v>1772.421039319847</v>
+        <v>1777.969718670473</v>
       </c>
       <c r="Y29" t="n">
-        <v>1483.211511357417</v>
+        <v>1488.760190708043</v>
       </c>
     </row>
     <row r="30">
@@ -6536,19 +6536,19 @@
         <v>435.8613981428639</v>
       </c>
       <c r="K30" t="n">
-        <v>847.8042142372474</v>
+        <v>643.9799167834981</v>
       </c>
       <c r="L30" t="n">
-        <v>1341.904675832448</v>
+        <v>1138.080378378698</v>
       </c>
       <c r="M30" t="n">
-        <v>1650.735217575307</v>
+        <v>1446.910920121557</v>
       </c>
       <c r="N30" t="n">
-        <v>2006.765502182875</v>
+        <v>1802.941204729126</v>
       </c>
       <c r="O30" t="n">
-        <v>2468.557953866594</v>
+        <v>2264.733656412845</v>
       </c>
       <c r="P30" t="n">
         <v>2600.013000882351</v>
@@ -6630,10 +6630,10 @@
         <v>425.5789893823512</v>
       </c>
       <c r="P31" t="n">
-        <v>425.5789893823512</v>
+        <v>81.36</v>
       </c>
       <c r="Q31" t="n">
-        <v>425.5789893823512</v>
+        <v>81.36</v>
       </c>
       <c r="R31" t="n">
         <v>81.36</v>
@@ -6667,25 +6667,25 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>1229.164925096351</v>
+        <v>1223.616245745725</v>
       </c>
       <c r="C32" t="n">
-        <v>1002.422926871105</v>
+        <v>996.8742475204788</v>
       </c>
       <c r="D32" t="n">
-        <v>815.2116584470142</v>
+        <v>809.6629790963881</v>
       </c>
       <c r="E32" t="n">
-        <v>634.0366184400762</v>
+        <v>628.48793908945</v>
       </c>
       <c r="F32" t="n">
-        <v>452.3299227754177</v>
+        <v>446.7812434247916</v>
       </c>
       <c r="G32" t="n">
-        <v>271.7669204653003</v>
+        <v>266.2182411146742</v>
       </c>
       <c r="H32" t="n">
-        <v>86.90867935062613</v>
+        <v>81.36</v>
       </c>
       <c r="I32" t="n">
         <v>81.36</v>
@@ -6727,16 +6727,16 @@
         <v>2975.450863729503</v>
       </c>
       <c r="V32" t="n">
-        <v>2566.510435278165</v>
+        <v>2560.961755927539</v>
       </c>
       <c r="W32" t="n">
-        <v>2148.961469640845</v>
+        <v>2143.412790290219</v>
       </c>
       <c r="X32" t="n">
-        <v>1777.969718670473</v>
+        <v>1772.421039319847</v>
       </c>
       <c r="Y32" t="n">
-        <v>1488.760190708043</v>
+        <v>1483.211511357417</v>
       </c>
     </row>
     <row r="33">
@@ -6770,22 +6770,22 @@
         <v>89.15487796756496</v>
       </c>
       <c r="J33" t="n">
-        <v>435.8613981428639</v>
+        <v>232.0371006891147</v>
       </c>
       <c r="K33" t="n">
-        <v>847.8042142372474</v>
+        <v>643.9799167834981</v>
       </c>
       <c r="L33" t="n">
-        <v>1341.904675832448</v>
+        <v>1138.080378378698</v>
       </c>
       <c r="M33" t="n">
-        <v>1650.735217575307</v>
+        <v>1446.910920121557</v>
       </c>
       <c r="N33" t="n">
-        <v>2006.765502182875</v>
+        <v>1802.941204729126</v>
       </c>
       <c r="O33" t="n">
-        <v>2468.557953866594</v>
+        <v>2264.733656412845</v>
       </c>
       <c r="P33" t="n">
         <v>2600.013000882351</v>
@@ -6867,7 +6867,7 @@
         <v>425.5789893823512</v>
       </c>
       <c r="P34" t="n">
-        <v>81.36</v>
+        <v>425.5789893823512</v>
       </c>
       <c r="Q34" t="n">
         <v>81.36</v>
@@ -6931,13 +6931,13 @@
         <v>436.0291130376557</v>
       </c>
       <c r="K35" t="n">
-        <v>733.1420762183976</v>
+        <v>989.4391130376558</v>
       </c>
       <c r="L35" t="n">
-        <v>733.1420762183976</v>
+        <v>1542.849113037656</v>
       </c>
       <c r="M35" t="n">
-        <v>1243.990904947333</v>
+        <v>1542.849113037656</v>
       </c>
       <c r="N35" t="n">
         <v>1797.400904947332</v>
@@ -6952,22 +6952,22 @@
         <v>2236</v>
       </c>
       <c r="R35" t="n">
-        <v>2236</v>
+        <v>2231.994554156147</v>
       </c>
       <c r="S35" t="n">
-        <v>2089.688719391593</v>
+        <v>2085.68327354774</v>
       </c>
       <c r="T35" t="n">
-        <v>1850.622475221327</v>
+        <v>1846.617029377474</v>
       </c>
       <c r="U35" t="n">
-        <v>1548.378741333841</v>
+        <v>1544.373295489988</v>
       </c>
       <c r="V35" t="n">
-        <v>1265.70093914513</v>
+        <v>1261.695493301277</v>
       </c>
       <c r="W35" t="n">
-        <v>974.4145997704354</v>
+        <v>970.4091539265823</v>
       </c>
       <c r="X35" t="n">
         <v>725.6800292188371</v>
@@ -6983,19 +6983,19 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>409.4673863086053</v>
+        <v>472.7782575464261</v>
       </c>
       <c r="C36" t="n">
-        <v>44.72</v>
+        <v>461.5662247731743</v>
       </c>
       <c r="D36" t="n">
-        <v>44.72</v>
+        <v>461.5662247731743</v>
       </c>
       <c r="E36" t="n">
-        <v>44.72</v>
+        <v>461.5662247731743</v>
       </c>
       <c r="F36" t="n">
-        <v>44.72</v>
+        <v>118.4993133207734</v>
       </c>
       <c r="G36" t="n">
         <v>44.72</v>
@@ -7062,16 +7062,16 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>870.0458296400257</v>
+        <v>877.7566123122328</v>
       </c>
       <c r="C37" t="n">
-        <v>946.5478354584615</v>
+        <v>954.2586181306687</v>
       </c>
       <c r="D37" t="n">
-        <v>1010.366979583462</v>
+        <v>1018.077762255669</v>
       </c>
       <c r="E37" t="n">
-        <v>1078.695883794875</v>
+        <v>1086.406666467082</v>
       </c>
       <c r="F37" t="n">
         <v>1153.55685638681</v>
@@ -7116,22 +7116,22 @@
         <v>44.72</v>
       </c>
       <c r="T37" t="n">
-        <v>175.5848964865977</v>
+        <v>183.2956791588049</v>
       </c>
       <c r="U37" t="n">
-        <v>372.6360891248843</v>
+        <v>380.3468717970915</v>
       </c>
       <c r="V37" t="n">
-        <v>521.9574820108303</v>
+        <v>529.6682646830375</v>
       </c>
       <c r="W37" t="n">
-        <v>644.3484002705077</v>
+        <v>652.0591829427149</v>
       </c>
       <c r="X37" t="n">
-        <v>745.8791912947012</v>
+        <v>753.5899739669084</v>
       </c>
       <c r="Y37" t="n">
-        <v>807.7884919737335</v>
+        <v>815.4992746459407</v>
       </c>
     </row>
     <row r="38">
@@ -7165,25 +7165,25 @@
         <v>44.72</v>
       </c>
       <c r="J38" t="n">
-        <v>436.0291130376557</v>
+        <v>44.72</v>
       </c>
       <c r="K38" t="n">
-        <v>436.0291130376557</v>
+        <v>598.13</v>
       </c>
       <c r="L38" t="n">
-        <v>436.0291130376557</v>
+        <v>1151.54</v>
       </c>
       <c r="M38" t="n">
-        <v>436.0291130376558</v>
+        <v>1151.54</v>
       </c>
       <c r="N38" t="n">
-        <v>690.5809049473327</v>
+        <v>1704.95</v>
       </c>
       <c r="O38" t="n">
-        <v>1243.990904947333</v>
+        <v>2236</v>
       </c>
       <c r="P38" t="n">
-        <v>1797.400904947332</v>
+        <v>2236</v>
       </c>
       <c r="Q38" t="n">
         <v>2236</v>
@@ -7192,25 +7192,25 @@
         <v>2236</v>
       </c>
       <c r="S38" t="n">
-        <v>2089.688719391593</v>
+        <v>2085.68327354774</v>
       </c>
       <c r="T38" t="n">
-        <v>1850.622475221327</v>
+        <v>1846.617029377474</v>
       </c>
       <c r="U38" t="n">
-        <v>1548.378741333841</v>
+        <v>1544.373295489988</v>
       </c>
       <c r="V38" t="n">
-        <v>1265.70093914513</v>
+        <v>1261.695493301277</v>
       </c>
       <c r="W38" t="n">
-        <v>974.4145997704354</v>
+        <v>970.4091539265823</v>
       </c>
       <c r="X38" t="n">
-        <v>729.6854750626902</v>
+        <v>725.6800292188371</v>
       </c>
       <c r="Y38" t="n">
-        <v>566.7385733628857</v>
+        <v>562.7331275190327</v>
       </c>
     </row>
     <row r="39">
@@ -7220,25 +7220,25 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>472.7782575464261</v>
+        <v>409.4673863086053</v>
       </c>
       <c r="C39" t="n">
-        <v>461.5662247731743</v>
+        <v>44.72</v>
       </c>
       <c r="D39" t="n">
-        <v>461.5662247731743</v>
+        <v>44.72</v>
       </c>
       <c r="E39" t="n">
-        <v>264.0395817084329</v>
+        <v>44.72</v>
       </c>
       <c r="F39" t="n">
-        <v>264.0395817084329</v>
+        <v>44.72</v>
       </c>
       <c r="G39" t="n">
-        <v>264.0395817084329</v>
+        <v>44.72</v>
       </c>
       <c r="H39" t="n">
-        <v>264.0395817084329</v>
+        <v>44.72</v>
       </c>
       <c r="I39" t="n">
         <v>44.72</v>
@@ -7274,22 +7274,22 @@
         <v>883.1445443513733</v>
       </c>
       <c r="T39" t="n">
-        <v>827.2276097882281</v>
+        <v>763.9167385504073</v>
       </c>
       <c r="U39" t="n">
-        <v>776.5100746769283</v>
+        <v>713.1992034391076</v>
       </c>
       <c r="V39" t="n">
-        <v>711.3477845844836</v>
+        <v>648.0369133466629</v>
       </c>
       <c r="W39" t="n">
-        <v>628.142589726071</v>
+        <v>564.8317184882503</v>
       </c>
       <c r="X39" t="n">
-        <v>557.5741660438614</v>
+        <v>494.2632948060406</v>
       </c>
       <c r="Y39" t="n">
-        <v>507.6838703204934</v>
+        <v>444.3729990826726</v>
       </c>
     </row>
     <row r="40">
@@ -7299,13 +7299,13 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>877.7566123122328</v>
+        <v>870.0458296400257</v>
       </c>
       <c r="C40" t="n">
-        <v>954.2586181306687</v>
+        <v>946.5478354584615</v>
       </c>
       <c r="D40" t="n">
-        <v>1018.077762255669</v>
+        <v>1010.366979583462</v>
       </c>
       <c r="E40" t="n">
         <v>1078.695883794875</v>
@@ -7362,13 +7362,13 @@
         <v>529.6682646830375</v>
       </c>
       <c r="W40" t="n">
-        <v>652.0591829427149</v>
+        <v>644.3484002705077</v>
       </c>
       <c r="X40" t="n">
-        <v>753.5899739669084</v>
+        <v>745.8791912947012</v>
       </c>
       <c r="Y40" t="n">
-        <v>815.4992746459407</v>
+        <v>807.7884919737335</v>
       </c>
     </row>
     <row r="41">
@@ -7378,46 +7378,46 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>433.4059340138206</v>
+        <v>429.4004881699675</v>
       </c>
       <c r="C41" t="n">
-        <v>332.9265620512004</v>
+        <v>328.9211162073474</v>
       </c>
       <c r="D41" t="n">
-        <v>271.977919889736</v>
+        <v>267.972474045883</v>
       </c>
       <c r="E41" t="n">
-        <v>217.0655061454243</v>
+        <v>213.0600603015712</v>
       </c>
       <c r="F41" t="n">
-        <v>161.6214367433921</v>
+        <v>157.615990899539</v>
       </c>
       <c r="G41" t="n">
-        <v>107.3210606959009</v>
+        <v>103.3156148520479</v>
       </c>
       <c r="H41" t="n">
-        <v>48.72544584385304</v>
+        <v>44.72</v>
       </c>
       <c r="I41" t="n">
         <v>44.72</v>
       </c>
       <c r="J41" t="n">
-        <v>436.0291130376557</v>
+        <v>44.72</v>
       </c>
       <c r="K41" t="n">
-        <v>436.0291130376557</v>
+        <v>598.13</v>
       </c>
       <c r="L41" t="n">
-        <v>436.0291130376557</v>
+        <v>1151.54</v>
       </c>
       <c r="M41" t="n">
-        <v>946.8779417665908</v>
+        <v>1662.388828728935</v>
       </c>
       <c r="N41" t="n">
-        <v>946.8779417665908</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="O41" t="n">
-        <v>1243.990904947333</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="P41" t="n">
         <v>1797.400904947332</v>
@@ -7426,28 +7426,28 @@
         <v>2236</v>
       </c>
       <c r="R41" t="n">
-        <v>2236</v>
+        <v>2231.994554156147</v>
       </c>
       <c r="S41" t="n">
-        <v>2089.688719391593</v>
+        <v>2085.68327354774</v>
       </c>
       <c r="T41" t="n">
-        <v>1850.622475221327</v>
+        <v>1846.617029377474</v>
       </c>
       <c r="U41" t="n">
-        <v>1548.378741333841</v>
+        <v>1544.373295489988</v>
       </c>
       <c r="V41" t="n">
-        <v>1265.70093914513</v>
+        <v>1261.695493301277</v>
       </c>
       <c r="W41" t="n">
-        <v>974.4145997704354</v>
+        <v>970.4091539265823</v>
       </c>
       <c r="X41" t="n">
-        <v>729.6854750626902</v>
+        <v>725.6800292188371</v>
       </c>
       <c r="Y41" t="n">
-        <v>566.7385733628857</v>
+        <v>562.7331275190327</v>
       </c>
     </row>
     <row r="42">
@@ -7457,22 +7457,22 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>55.93203277325181</v>
+        <v>391.4553531635761</v>
       </c>
       <c r="C42" t="n">
-        <v>44.72</v>
+        <v>380.2433203903244</v>
       </c>
       <c r="D42" t="n">
-        <v>44.72</v>
+        <v>380.2433203903244</v>
       </c>
       <c r="E42" t="n">
-        <v>44.72</v>
+        <v>380.2433203903244</v>
       </c>
       <c r="F42" t="n">
-        <v>44.72</v>
+        <v>380.2433203903244</v>
       </c>
       <c r="G42" t="n">
-        <v>44.72</v>
+        <v>380.2433203903244</v>
       </c>
       <c r="H42" t="n">
         <v>44.72</v>
@@ -7505,28 +7505,28 @@
         <v>1200.152420368536</v>
       </c>
       <c r="R42" t="n">
-        <v>647.3506049216877</v>
+        <v>919.5630540741914</v>
       </c>
       <c r="S42" t="n">
-        <v>466.2983195781991</v>
+        <v>801.8216399685234</v>
       </c>
       <c r="T42" t="n">
-        <v>410.3813850150538</v>
+        <v>745.9047054053782</v>
       </c>
       <c r="U42" t="n">
-        <v>359.6638499037541</v>
+        <v>695.1871702940784</v>
       </c>
       <c r="V42" t="n">
-        <v>294.5015598113094</v>
+        <v>630.0248802016338</v>
       </c>
       <c r="W42" t="n">
-        <v>211.2963649528968</v>
+        <v>546.8196853432211</v>
       </c>
       <c r="X42" t="n">
-        <v>140.7279412706871</v>
+        <v>476.2512616610114</v>
       </c>
       <c r="Y42" t="n">
-        <v>90.8376455473191</v>
+        <v>426.3609659376434</v>
       </c>
     </row>
     <row r="43">
@@ -7615,10 +7615,10 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>429.4004881699675</v>
+        <v>433.4059340138206</v>
       </c>
       <c r="C44" t="n">
-        <v>328.9211162073474</v>
+        <v>332.9265620512004</v>
       </c>
       <c r="D44" t="n">
         <v>267.972474045883</v>
@@ -7642,13 +7642,13 @@
         <v>436.0291130376557</v>
       </c>
       <c r="K44" t="n">
-        <v>733.1420762183976</v>
+        <v>989.4391130376558</v>
       </c>
       <c r="L44" t="n">
-        <v>733.1420762183976</v>
+        <v>1542.849113037656</v>
       </c>
       <c r="M44" t="n">
-        <v>1243.990904947333</v>
+        <v>1797.400904947332</v>
       </c>
       <c r="N44" t="n">
         <v>1797.400904947332</v>
@@ -7669,22 +7669,22 @@
         <v>2089.688719391593</v>
       </c>
       <c r="T44" t="n">
-        <v>1846.617029377474</v>
+        <v>1850.622475221327</v>
       </c>
       <c r="U44" t="n">
-        <v>1544.373295489988</v>
+        <v>1548.378741333841</v>
       </c>
       <c r="V44" t="n">
-        <v>1261.695493301277</v>
+        <v>1265.70093914513</v>
       </c>
       <c r="W44" t="n">
-        <v>970.4091539265823</v>
+        <v>974.4145997704354</v>
       </c>
       <c r="X44" t="n">
-        <v>725.6800292188371</v>
+        <v>729.6854750626902</v>
       </c>
       <c r="Y44" t="n">
-        <v>562.7331275190327</v>
+        <v>566.7385733628857</v>
       </c>
     </row>
     <row r="45">
@@ -7694,16 +7694,16 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>119.2429040110725</v>
+        <v>398.9989442256527</v>
       </c>
       <c r="C45" t="n">
-        <v>44.72</v>
+        <v>387.7869114524009</v>
       </c>
       <c r="D45" t="n">
-        <v>44.72</v>
+        <v>387.7869114524009</v>
       </c>
       <c r="E45" t="n">
-        <v>44.72</v>
+        <v>387.7869114524009</v>
       </c>
       <c r="F45" t="n">
         <v>44.72</v>
@@ -7745,25 +7745,25 @@
         <v>1000.885958457041</v>
       </c>
       <c r="S45" t="n">
-        <v>529.6091908160197</v>
+        <v>883.1445443513733</v>
       </c>
       <c r="T45" t="n">
-        <v>473.6922562528744</v>
+        <v>827.2276097882281</v>
       </c>
       <c r="U45" t="n">
-        <v>422.9747211415747</v>
+        <v>702.730761356155</v>
       </c>
       <c r="V45" t="n">
-        <v>357.8124310491301</v>
+        <v>637.5684712637103</v>
       </c>
       <c r="W45" t="n">
-        <v>274.6072361907174</v>
+        <v>554.3632764052976</v>
       </c>
       <c r="X45" t="n">
-        <v>204.0388125085078</v>
+        <v>483.794852723088</v>
       </c>
       <c r="Y45" t="n">
-        <v>154.1485167851397</v>
+        <v>433.9045569997199</v>
       </c>
     </row>
     <row r="46">
@@ -8210,13 +8210,13 @@
         <v>369.4444444444445</v>
       </c>
       <c r="M5" t="n">
-        <v>544.2621276423173</v>
+        <v>929.2621276423173</v>
       </c>
       <c r="N5" t="n">
         <v>862.2489580698352</v>
       </c>
       <c r="O5" t="n">
-        <v>455.2478695740924</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P5" t="n">
         <v>0.2870600406814136</v>
@@ -8444,16 +8444,16 @@
         <v>385</v>
       </c>
       <c r="L8" t="n">
-        <v>369.4444444444445</v>
+        <v>385</v>
       </c>
       <c r="M8" t="n">
-        <v>929.2621276423173</v>
+        <v>913.7065720867616</v>
       </c>
       <c r="N8" t="n">
-        <v>862.2489580698352</v>
+        <v>477.2489580698352</v>
       </c>
       <c r="O8" t="n">
-        <v>70.24786957409245</v>
+        <v>455.2478695740924</v>
       </c>
       <c r="P8" t="n">
         <v>0.2870600406814136</v>
@@ -8678,25 +8678,25 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K11" t="n">
-        <v>716.8751175230994</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>916.1914086561842</v>
+        <v>382.9934426543497</v>
       </c>
       <c r="M11" t="n">
-        <v>1060.271045550332</v>
+        <v>544.2621276423173</v>
       </c>
       <c r="N11" t="n">
-        <v>997.1516381647463</v>
+        <v>1096.663422488788</v>
       </c>
       <c r="O11" t="n">
-        <v>1032.917105959907</v>
+        <v>986.2478695740924</v>
       </c>
       <c r="P11" t="n">
-        <v>0.2870600406814136</v>
+        <v>870.5779326741233</v>
       </c>
       <c r="Q11" t="n">
-        <v>172.8226843274854</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R11" t="n">
         <v>294.54111633436</v>
@@ -8912,13 +8912,13 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J14" t="n">
-        <v>430.3047365861567</v>
+        <v>35.04300624509033</v>
       </c>
       <c r="K14" t="n">
-        <v>716.8751175230994</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>916.1914086561842</v>
+        <v>262.2462550874009</v>
       </c>
       <c r="M14" t="n">
         <v>1060.271045550332</v>
@@ -8927,10 +8927,10 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O14" t="n">
-        <v>490.3759326937771</v>
+        <v>986.2478695740924</v>
       </c>
       <c r="P14" t="n">
-        <v>0.2870600406814136</v>
+        <v>870.5779326741233</v>
       </c>
       <c r="Q14" t="n">
         <v>615.8520732695737</v>
@@ -9149,28 +9149,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J17" t="n">
-        <v>330.7929522621153</v>
+        <v>430.3047365861567</v>
       </c>
       <c r="K17" t="n">
         <v>716.8751175230994</v>
       </c>
       <c r="L17" t="n">
-        <v>916.1914086561842</v>
+        <v>582.1183251312507</v>
       </c>
       <c r="M17" t="n">
-        <v>1060.271045550332</v>
+        <v>544.2621276423173</v>
       </c>
       <c r="N17" t="n">
         <v>1096.663422488788</v>
       </c>
       <c r="O17" t="n">
-        <v>1032.917105959907</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P17" t="n">
-        <v>0.2870600406814136</v>
+        <v>870.5779326741233</v>
       </c>
       <c r="Q17" t="n">
-        <v>172.8226843274854</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R17" t="n">
         <v>294.54111633436</v>
@@ -9389,10 +9389,10 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L20" t="n">
-        <v>220.2344802797121</v>
+        <v>66.10940722323539</v>
       </c>
       <c r="M20" t="n">
         <v>1060.271045550332</v>
@@ -9401,7 +9401,7 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O20" t="n">
-        <v>1032.917105959907</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P20" t="n">
         <v>870.5779326741233</v>
@@ -9626,10 +9626,10 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K23" t="n">
-        <v>716.8751175230994</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>916.1914086561842</v>
+        <v>310.0139136884231</v>
       </c>
       <c r="M23" t="n">
         <v>1060.271045550332</v>
@@ -9638,13 +9638,13 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O23" t="n">
-        <v>490.3759326937771</v>
+        <v>986.2478695740924</v>
       </c>
       <c r="P23" t="n">
-        <v>0.2870600406814136</v>
+        <v>870.5779326741233</v>
       </c>
       <c r="Q23" t="n">
-        <v>615.8520732695737</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R23" t="n">
         <v>294.54111633436</v>
@@ -9866,7 +9866,7 @@
         <v>716.8751175230994</v>
       </c>
       <c r="L26" t="n">
-        <v>466.0285991424271</v>
+        <v>916.1914086561842</v>
       </c>
       <c r="M26" t="n">
         <v>1060.271045550332</v>
@@ -9875,10 +9875,10 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O26" t="n">
-        <v>70.24786957409245</v>
+        <v>490.3759326937771</v>
       </c>
       <c r="P26" t="n">
-        <v>870.5779326741233</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q26" t="n">
         <v>615.8520732695737</v>
@@ -10097,25 +10097,25 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J29" t="n">
-        <v>430.3047365861567</v>
+        <v>35.04300624509033</v>
       </c>
       <c r="K29" t="n">
         <v>716.8751175230994</v>
       </c>
       <c r="L29" t="n">
-        <v>916.1914086561842</v>
+        <v>861.2903294834937</v>
       </c>
       <c r="M29" t="n">
-        <v>544.2621276423173</v>
+        <v>1060.271045550332</v>
       </c>
       <c r="N29" t="n">
         <v>1096.663422488788</v>
       </c>
       <c r="O29" t="n">
-        <v>1006.384850601792</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P29" t="n">
-        <v>0.2870600406814136</v>
+        <v>870.5779326741233</v>
       </c>
       <c r="Q29" t="n">
         <v>615.8520732695737</v>
@@ -10574,16 +10574,16 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K35" t="n">
-        <v>300.1141042229715</v>
+        <v>559</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="M35" t="n">
-        <v>1060.271045550332</v>
+        <v>544.2621276423173</v>
       </c>
       <c r="N35" t="n">
-        <v>1036.248958069835</v>
+        <v>734.3719802008218</v>
       </c>
       <c r="O35" t="n">
         <v>70.24786957409245</v>
@@ -10808,28 +10808,28 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J38" t="n">
-        <v>430.3047365861567</v>
+        <v>35.04300624509033</v>
       </c>
       <c r="K38" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>559.0000000000001</v>
       </c>
       <c r="M38" t="n">
         <v>544.2621276423173</v>
       </c>
       <c r="N38" t="n">
-        <v>734.371980200822</v>
+        <v>1036.248958069835</v>
       </c>
       <c r="O38" t="n">
-        <v>629.2478695740924</v>
+        <v>606.6620109882336</v>
       </c>
       <c r="P38" t="n">
-        <v>559.2870600406815</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q38" t="n">
-        <v>615.8520732695737</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R38" t="n">
         <v>294.54111633436</v>
@@ -11045,25 +11045,25 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J41" t="n">
-        <v>430.3047365861567</v>
+        <v>35.04300624509033</v>
       </c>
       <c r="K41" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>559.0000000000001</v>
       </c>
       <c r="M41" t="n">
         <v>1060.271045550332</v>
       </c>
       <c r="N41" t="n">
-        <v>477.2489580698352</v>
+        <v>613.624792633873</v>
       </c>
       <c r="O41" t="n">
-        <v>370.361973797064</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P41" t="n">
-        <v>559.2870600406815</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q41" t="n">
         <v>615.8520732695737</v>
@@ -11285,16 +11285,16 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K44" t="n">
-        <v>300.1141042229715</v>
+        <v>559</v>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="M44" t="n">
-        <v>1060.271045550332</v>
+        <v>801.3851497733039</v>
       </c>
       <c r="N44" t="n">
-        <v>1036.248958069835</v>
+        <v>477.2489580698352</v>
       </c>
       <c r="O44" t="n">
         <v>70.24786957409245</v>
@@ -22700,7 +22700,7 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.591170646055957</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -22718,7 +22718,7 @@
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.591170646055787</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -22937,7 +22937,7 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.591170646055957</v>
       </c>
       <c r="M7" t="n">
         <v>0</v>
@@ -22955,7 +22955,7 @@
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.591170646055787</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -23174,7 +23174,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.591170646055957</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
@@ -23192,7 +23192,7 @@
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.591170646055787</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -23381,22 +23381,22 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>62.11380033707866</v>
+        <v>36.11380033707866</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>21.72524664804467</v>
       </c>
       <c r="D13" t="n">
-        <v>60.53621805555548</v>
+        <v>34.53621805555548</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>29.98090483695654</v>
       </c>
       <c r="F13" t="n">
-        <v>49.38285596774193</v>
+        <v>23.38285596774193</v>
       </c>
       <c r="G13" t="n">
-        <v>20.04387284153003</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -23408,31 +23408,31 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>63.52077380114304</v>
+        <v>37.52077380114304</v>
       </c>
       <c r="L13" t="n">
-        <v>198.5476281577792</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>58.56096339902345</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>346.1850752716849</v>
+        <v>320.1850752716849</v>
       </c>
       <c r="O13" t="n">
-        <v>415.445564079015</v>
+        <v>389.445564079015</v>
       </c>
       <c r="P13" t="n">
-        <v>462.4478973282775</v>
+        <v>436.4478973282775</v>
       </c>
       <c r="Q13" t="n">
-        <v>500.839266425598</v>
+        <v>424.9033116796812</v>
       </c>
       <c r="R13" t="n">
-        <v>501.6021279811511</v>
+        <v>475.6021279811511</v>
       </c>
       <c r="S13" t="n">
-        <v>137.3734797028554</v>
+        <v>111.3734797028554</v>
       </c>
       <c r="T13" t="n">
         <v>0</v>
@@ -23447,10 +23447,10 @@
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>22.44364543010755</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>62.46535284946236</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -23618,22 +23618,22 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>62.11380033707866</v>
+        <v>36.11380033707866</v>
       </c>
       <c r="C16" t="n">
-        <v>47.72524664804467</v>
+        <v>21.72524664804467</v>
       </c>
       <c r="D16" t="n">
-        <v>60.53621805555548</v>
+        <v>34.53621805555548</v>
       </c>
       <c r="E16" t="n">
-        <v>55.98090483695654</v>
+        <v>29.98090483695654</v>
       </c>
       <c r="F16" t="n">
-        <v>49.38285596774193</v>
+        <v>23.38285596774193</v>
       </c>
       <c r="G16" t="n">
-        <v>20.04387284153003</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
@@ -23645,31 +23645,31 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>63.52077380114304</v>
+        <v>37.52077380114304</v>
       </c>
       <c r="L16" t="n">
-        <v>198.5476281577792</v>
+        <v>172.5476281577792</v>
       </c>
       <c r="M16" t="n">
-        <v>295.6316114025499</v>
+        <v>269.6316114025499</v>
       </c>
       <c r="N16" t="n">
-        <v>346.1850752716849</v>
+        <v>320.1850752716849</v>
       </c>
       <c r="O16" t="n">
-        <v>415.445564079015</v>
+        <v>389.445564079015</v>
       </c>
       <c r="P16" t="n">
-        <v>462.4478973282775</v>
+        <v>436.4478973282775</v>
       </c>
       <c r="Q16" t="n">
-        <v>500.839266425598</v>
+        <v>421.8608472510409</v>
       </c>
       <c r="R16" t="n">
-        <v>320.6424536255864</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>111.3734797028554</v>
       </c>
       <c r="T16" t="n">
         <v>0</v>
@@ -23687,7 +23687,7 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>62.46535284946236</v>
+        <v>36.46535284946236</v>
       </c>
     </row>
     <row r="17">
@@ -23855,19 +23855,19 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>36.11380033707866</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>21.72524664804467</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>34.53621805555548</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>29.98090483695654</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>23.38285596774193</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -23882,31 +23882,31 @@
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>63.52077380114304</v>
+        <v>37.52077380114304</v>
       </c>
       <c r="L19" t="n">
-        <v>198.5476281577792</v>
+        <v>172.5476281577792</v>
       </c>
       <c r="M19" t="n">
-        <v>295.6316114025499</v>
+        <v>269.6316114025499</v>
       </c>
       <c r="N19" t="n">
-        <v>346.1850752716849</v>
+        <v>320.1850752716849</v>
       </c>
       <c r="O19" t="n">
-        <v>415.445564079015</v>
+        <v>389.445564079015</v>
       </c>
       <c r="P19" t="n">
-        <v>462.4478973282775</v>
+        <v>436.4478973282775</v>
       </c>
       <c r="Q19" t="n">
-        <v>500.839266425598</v>
+        <v>421.8608472510409</v>
       </c>
       <c r="R19" t="n">
-        <v>501.6021279811511</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>137.3734797028554</v>
+        <v>111.3734797028554</v>
       </c>
       <c r="T19" t="n">
         <v>0</v>
@@ -23921,10 +23921,10 @@
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>22.44364543010755</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>17.47145204784202</v>
+        <v>36.46535284946236</v>
       </c>
     </row>
     <row r="20">
@@ -24092,22 +24092,22 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0</v>
+        <v>36.11380033707866</v>
       </c>
       <c r="C22" t="n">
-        <v>47.72524664804467</v>
+        <v>21.72524664804467</v>
       </c>
       <c r="D22" t="n">
-        <v>60.53621805555548</v>
+        <v>34.53621805555548</v>
       </c>
       <c r="E22" t="n">
-        <v>55.98090483695654</v>
+        <v>29.98090483695654</v>
       </c>
       <c r="F22" t="n">
-        <v>49.38285596774193</v>
+        <v>23.38285596774193</v>
       </c>
       <c r="G22" t="n">
-        <v>20.04387284153003</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
         <v>0</v>
@@ -24119,31 +24119,31 @@
         <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>63.52077380114304</v>
+        <v>37.52077380114304</v>
       </c>
       <c r="L22" t="n">
-        <v>198.5476281577792</v>
+        <v>172.5476281577792</v>
       </c>
       <c r="M22" t="n">
-        <v>295.6316114025499</v>
+        <v>269.6316114025499</v>
       </c>
       <c r="N22" t="n">
-        <v>346.1850752716849</v>
+        <v>320.1850752716849</v>
       </c>
       <c r="O22" t="n">
-        <v>415.445564079015</v>
+        <v>389.445564079015</v>
       </c>
       <c r="P22" t="n">
-        <v>462.4478973282775</v>
+        <v>382.7066165981672</v>
       </c>
       <c r="Q22" t="n">
-        <v>500.839266425598</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>445.2216068121274</v>
+        <v>475.6021279811511</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>111.3734797028554</v>
       </c>
       <c r="T22" t="n">
         <v>0</v>
@@ -24161,7 +24161,7 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>36.46535284946236</v>
       </c>
     </row>
     <row r="23">
@@ -24329,22 +24329,22 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0</v>
+        <v>36.11380033707866</v>
       </c>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>21.72524664804467</v>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>34.53621805555548</v>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>29.98090483695654</v>
       </c>
       <c r="F25" t="n">
-        <v>19.8712246364196</v>
+        <v>23.38285596774193</v>
       </c>
       <c r="G25" t="n">
-        <v>20.04387284153003</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
@@ -24356,31 +24356,31 @@
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>63.52077380114304</v>
+        <v>37.52077380114304</v>
       </c>
       <c r="L25" t="n">
-        <v>198.5476281577792</v>
+        <v>172.5476281577792</v>
       </c>
       <c r="M25" t="n">
-        <v>295.6316114025499</v>
+        <v>269.6316114025499</v>
       </c>
       <c r="N25" t="n">
-        <v>346.1850752716849</v>
+        <v>320.1850752716849</v>
       </c>
       <c r="O25" t="n">
-        <v>415.445564079015</v>
+        <v>389.445564079015</v>
       </c>
       <c r="P25" t="n">
-        <v>462.4478973282775</v>
+        <v>436.4478973282775</v>
       </c>
       <c r="Q25" t="n">
-        <v>500.839266425598</v>
+        <v>421.8608472510409</v>
       </c>
       <c r="R25" t="n">
-        <v>501.6021279811511</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>137.3734797028554</v>
+        <v>111.3734797028554</v>
       </c>
       <c r="T25" t="n">
         <v>0</v>
@@ -24398,7 +24398,7 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>36.46535284946236</v>
       </c>
     </row>
     <row r="26">
@@ -24605,7 +24605,7 @@
         <v>346.1850752716849</v>
       </c>
       <c r="O28" t="n">
-        <v>74.66876459048729</v>
+        <v>415.445564079015</v>
       </c>
       <c r="P28" t="n">
         <v>462.4478973282775</v>
@@ -24614,7 +24614,7 @@
         <v>500.839266425598</v>
       </c>
       <c r="R28" t="n">
-        <v>501.6021279811511</v>
+        <v>160.8253284926234</v>
       </c>
       <c r="S28" t="n">
         <v>137.3734797028554</v>
@@ -24845,13 +24845,13 @@
         <v>415.445564079015</v>
       </c>
       <c r="P31" t="n">
-        <v>462.4478973282775</v>
+        <v>121.6710978397498</v>
       </c>
       <c r="Q31" t="n">
         <v>500.839266425598</v>
       </c>
       <c r="R31" t="n">
-        <v>160.8253284926234</v>
+        <v>501.6021279811511</v>
       </c>
       <c r="S31" t="n">
         <v>137.3734797028554</v>
@@ -25082,10 +25082,10 @@
         <v>415.445564079015</v>
       </c>
       <c r="P34" t="n">
-        <v>121.6710978397498</v>
+        <v>462.4478973282775</v>
       </c>
       <c r="Q34" t="n">
-        <v>500.839266425598</v>
+        <v>160.0624669370703</v>
       </c>
       <c r="R34" t="n">
         <v>501.6021279811511</v>
@@ -26110,7 +26110,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4182269.175270728</v>
+        <v>4189775.907184802</v>
       </c>
     </row>
     <row r="6">
@@ -26118,7 +26118,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5162617.364816885</v>
+        <v>5182405.863796547</v>
       </c>
     </row>
     <row r="7">
@@ -26126,7 +26126,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>6142965.55436304</v>
+        <v>6175035.82040829</v>
       </c>
     </row>
     <row r="8">
@@ -26134,7 +26134,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7123313.743909192</v>
+        <v>7167665.777020029</v>
       </c>
     </row>
     <row r="9">
@@ -26142,7 +26142,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8103661.933455345</v>
+        <v>8160295.733631768</v>
       </c>
     </row>
     <row r="10">
@@ -26150,7 +26150,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9084010.123001499</v>
+        <v>9145418.958329435</v>
       </c>
     </row>
     <row r="11">
@@ -26158,7 +26158,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>10064358.31254765</v>
+        <v>10125767.14787559</v>
       </c>
     </row>
     <row r="12">
@@ -26166,7 +26166,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>11044706.5020938</v>
+        <v>11106115.33742174</v>
       </c>
     </row>
     <row r="13">
@@ -26174,7 +26174,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>12062039.43067123</v>
+        <v>12123448.26599917</v>
       </c>
     </row>
     <row r="14">
@@ -26182,7 +26182,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>13101025.48894563</v>
+        <v>13162434.32427356</v>
       </c>
     </row>
     <row r="15">
@@ -26190,7 +26190,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>14140011.54722002</v>
+        <v>14201420.38254796</v>
       </c>
     </row>
     <row r="16">
@@ -26198,7 +26198,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>15178997.60549442</v>
+        <v>15240406.44082236</v>
       </c>
     </row>
   </sheetData>
@@ -26278,19 +26278,19 @@
         <v>1164888.438319308</v>
       </c>
       <c r="E2" t="n">
-        <v>1099178.273127508</v>
+        <v>1112948.73923135</v>
       </c>
       <c r="F2" t="n">
-        <v>1099178.273127508</v>
+        <v>1112948.739231349</v>
       </c>
       <c r="G2" t="n">
-        <v>1099178.273127508</v>
+        <v>1112948.739231349</v>
       </c>
       <c r="H2" t="n">
-        <v>1099178.273127508</v>
+        <v>1112948.73923135</v>
       </c>
       <c r="I2" t="n">
-        <v>1099178.273127508</v>
+        <v>1112948.739231349</v>
       </c>
       <c r="J2" t="n">
         <v>1099178.273127508</v>
@@ -26305,10 +26305,10 @@
         <v>1164923.76230765</v>
       </c>
       <c r="N2" t="n">
-        <v>1164923.762307649</v>
+        <v>1164923.76230765</v>
       </c>
       <c r="O2" t="n">
-        <v>1164923.762307649</v>
+        <v>1164923.76230765</v>
       </c>
       <c r="P2" t="n">
         <v>1164923.76230765</v>
@@ -26330,7 +26330,7 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>402464</v>
+        <v>387712</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -26345,7 +26345,7 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>315520</v>
+        <v>351072</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -26354,7 +26354,7 @@
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>161248</v>
+        <v>125696</v>
       </c>
       <c r="N3" t="n">
         <v>0</v>
@@ -26373,49 +26373,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>570914.1248995091</v>
+        <v>572429.9805878249</v>
       </c>
       <c r="C4" t="n">
-        <v>568856.1447656949</v>
+        <v>570372.0004540107</v>
       </c>
       <c r="D4" t="n">
-        <v>566795.372853379</v>
+        <v>568311.2285416948</v>
       </c>
       <c r="E4" t="n">
-        <v>445852.6895118617</v>
+        <v>468964.8457662077</v>
       </c>
       <c r="F4" t="n">
-        <v>444399.1387482317</v>
+        <v>467405.5293950558</v>
       </c>
       <c r="G4" t="n">
-        <v>442943.5821390834</v>
+        <v>465844.0612258157</v>
       </c>
       <c r="H4" t="n">
-        <v>441486.0053004215</v>
+        <v>464280.4258278603</v>
       </c>
       <c r="I4" t="n">
-        <v>440026.3936608351</v>
+        <v>462714.6075695099</v>
       </c>
       <c r="J4" t="n">
-        <v>438564.7324579426</v>
+        <v>440901.4403696402</v>
       </c>
       <c r="K4" t="n">
-        <v>437101.0067347542</v>
+        <v>439437.7146464518</v>
       </c>
       <c r="L4" t="n">
-        <v>435635.201335937</v>
+        <v>437971.9092476347</v>
       </c>
       <c r="M4" t="n">
-        <v>527474.7245421007</v>
+        <v>529216.5743552083</v>
       </c>
       <c r="N4" t="n">
-        <v>525509.8275072473</v>
+        <v>527251.677320355</v>
       </c>
       <c r="O4" t="n">
-        <v>523542.0882495092</v>
+        <v>525283.9380626169</v>
       </c>
       <c r="P4" t="n">
-        <v>521571.4853984989</v>
+        <v>523313.3352116066</v>
       </c>
     </row>
     <row r="5">
@@ -26434,19 +26434,19 @@
         <v>57035.6</v>
       </c>
       <c r="E5" t="n">
-        <v>80749.125</v>
+        <v>76794.11899999999</v>
       </c>
       <c r="F5" t="n">
-        <v>80749.125</v>
+        <v>76794.11899999999</v>
       </c>
       <c r="G5" t="n">
-        <v>80749.125</v>
+        <v>76794.11899999999</v>
       </c>
       <c r="H5" t="n">
-        <v>80749.125</v>
+        <v>76794.11899999999</v>
       </c>
       <c r="I5" t="n">
-        <v>80749.125</v>
+        <v>76794.11899999999</v>
       </c>
       <c r="J5" t="n">
         <v>80749.125</v>
@@ -26477,49 +26477,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>401418.7134197986</v>
+        <v>399902.8577314831</v>
       </c>
       <c r="C6" t="n">
-        <v>538996.6935536127</v>
+        <v>537480.8378652971</v>
       </c>
       <c r="D6" t="n">
-        <v>541057.4654659288</v>
+        <v>539541.6097776127</v>
       </c>
       <c r="E6" t="n">
-        <v>170112.4586156462</v>
+        <v>179477.7744651419</v>
       </c>
       <c r="F6" t="n">
-        <v>574030.0093792767</v>
+        <v>568749.0908362934</v>
       </c>
       <c r="G6" t="n">
-        <v>575485.5659884249</v>
+        <v>570310.5590055336</v>
       </c>
       <c r="H6" t="n">
-        <v>576943.1428270862</v>
+        <v>571874.1944034895</v>
       </c>
       <c r="I6" t="n">
-        <v>578402.7544666732</v>
+        <v>573440.0126618394</v>
       </c>
       <c r="J6" t="n">
-        <v>264344.4156695655</v>
+        <v>226455.7077578681</v>
       </c>
       <c r="K6" t="n">
-        <v>581328.1413927537</v>
+        <v>578991.4334810565</v>
       </c>
       <c r="L6" t="n">
-        <v>582793.9467915711</v>
+        <v>580457.2388798737</v>
       </c>
       <c r="M6" t="n">
-        <v>412789.6877655491</v>
+        <v>446599.8379524417</v>
       </c>
       <c r="N6" t="n">
-        <v>576002.5848004019</v>
+        <v>574260.7349872948</v>
       </c>
       <c r="O6" t="n">
-        <v>397970.3240581403</v>
+        <v>396228.4742450329</v>
       </c>
       <c r="P6" t="n">
-        <v>579940.9269091508</v>
+        <v>578199.0770960433</v>
       </c>
     </row>
   </sheetData>
@@ -26764,19 +26764,19 @@
         <v>400</v>
       </c>
       <c r="E2" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="F2" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="G2" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="H2" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="I2" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="J2" t="n">
         <v>225</v>
@@ -26868,19 +26868,19 @@
         <v>385</v>
       </c>
       <c r="E4" t="n">
-        <v>1017</v>
+        <v>916</v>
       </c>
       <c r="F4" t="n">
-        <v>1017</v>
+        <v>916</v>
       </c>
       <c r="G4" t="n">
-        <v>1017</v>
+        <v>916</v>
       </c>
       <c r="H4" t="n">
-        <v>1017</v>
+        <v>916</v>
       </c>
       <c r="I4" t="n">
-        <v>1017</v>
+        <v>916</v>
       </c>
       <c r="J4" t="n">
         <v>1017</v>
@@ -26981,10 +26981,10 @@
         <v>-0</v>
       </c>
       <c r="E2" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="F2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G2" t="n">
         <v>-0</v>
@@ -26999,10 +26999,10 @@
         <v>225</v>
       </c>
       <c r="K2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
         <v>125</v>
@@ -27033,16 +27033,16 @@
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G3" t="n">
         <v>-0</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -27051,7 +27051,7 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -27060,10 +27060,10 @@
         <v>-0</v>
       </c>
       <c r="N3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
         <v>-0</v>
@@ -27085,7 +27085,7 @@
         <v>-0</v>
       </c>
       <c r="E4" t="n">
-        <v>632</v>
+        <v>531</v>
       </c>
       <c r="F4" t="n">
         <v>-0</v>
@@ -27100,7 +27100,7 @@
         <v>-0</v>
       </c>
       <c r="J4" t="n">
-        <v>385</v>
+        <v>486</v>
       </c>
       <c r="K4" t="n">
         <v>-0</v>
@@ -27109,7 +27109,7 @@
         <v>-0</v>
       </c>
       <c r="M4" t="n">
-        <v>174</v>
+        <v>73</v>
       </c>
       <c r="N4" t="n">
         <v>-0</v>
@@ -27213,7 +27213,7 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
@@ -27326,7 +27326,7 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>632</v>
+        <v>531</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
@@ -27454,7 +27454,7 @@
         <v>400</v>
       </c>
       <c r="I2" t="n">
-        <v>150.0811596826846</v>
+        <v>121.3749682972702</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -27484,7 +27484,7 @@
         <v>250.8785988282945</v>
       </c>
       <c r="S2" t="n">
-        <v>371.2938086145853</v>
+        <v>400</v>
       </c>
       <c r="T2" t="n">
         <v>400</v>
@@ -27515,7 +27515,7 @@
         <v>384.5565566463266</v>
       </c>
       <c r="C3" t="n">
-        <v>219.3194749189519</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D3" t="n">
         <v>347.9376868977026</v>
@@ -27524,16 +27524,16 @@
         <v>342.6720972219126</v>
       </c>
       <c r="F3" t="n">
-        <v>339.6362423378769</v>
+        <v>198.8683453806883</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>325.7395358750273</v>
       </c>
       <c r="H3" t="n">
-        <v>332.1680871864211</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>217.1263858913485</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
@@ -27557,7 +27557,7 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R3" t="n">
         <v>400</v>
@@ -27569,7 +27569,7 @@
         <v>400</v>
       </c>
       <c r="U3" t="n">
-        <v>400</v>
+        <v>15.21035976018675</v>
       </c>
       <c r="V3" t="n">
         <v>400</v>
@@ -27597,13 +27597,13 @@
         <v>400</v>
       </c>
       <c r="D4" t="n">
-        <v>316.4991679299849</v>
+        <v>400</v>
       </c>
       <c r="E4" t="n">
-        <v>280.9809048369565</v>
+        <v>400</v>
       </c>
       <c r="F4" t="n">
-        <v>274.3828559677419</v>
+        <v>400</v>
       </c>
       <c r="G4" t="n">
         <v>245.04387284153</v>
@@ -27645,16 +27645,16 @@
         <v>362.3734797028554</v>
       </c>
       <c r="T4" t="n">
-        <v>210.0245665062577</v>
+        <v>400</v>
       </c>
       <c r="U4" t="n">
-        <v>400</v>
+        <v>150.9583912744579</v>
       </c>
       <c r="V4" t="n">
-        <v>400</v>
+        <v>199.1703102162162</v>
       </c>
       <c r="W4" t="n">
-        <v>400</v>
+        <v>331.7587937502667</v>
       </c>
       <c r="X4" t="n">
         <v>400</v>
@@ -27688,7 +27688,7 @@
         <v>400</v>
       </c>
       <c r="H5" t="n">
-        <v>371.2938086145855</v>
+        <v>400</v>
       </c>
       <c r="I5" t="n">
         <v>150.0811596826846</v>
@@ -27724,7 +27724,7 @@
         <v>400</v>
       </c>
       <c r="T5" t="n">
-        <v>400</v>
+        <v>371.2938086145853</v>
       </c>
       <c r="U5" t="n">
         <v>400</v>
@@ -27755,22 +27755,22 @@
         <v>361.0999124455193</v>
       </c>
       <c r="D6" t="n">
-        <v>347.9376868977026</v>
+        <v>155.587840727184</v>
       </c>
       <c r="E6" t="n">
         <v>342.6720972219126</v>
       </c>
       <c r="F6" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>17.3083845693742</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>332.1680871864211</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>217.1263858913485</v>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -27828,34 +27828,34 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>400</v>
+        <v>287.1138003370787</v>
       </c>
       <c r="C7" t="n">
-        <v>400</v>
+        <v>272.7252466480447</v>
       </c>
       <c r="D7" t="n">
-        <v>400</v>
+        <v>285.5362180555555</v>
       </c>
       <c r="E7" t="n">
-        <v>400</v>
+        <v>341.3041813133401</v>
       </c>
       <c r="F7" t="n">
         <v>400</v>
       </c>
       <c r="G7" t="n">
-        <v>281.6378527403057</v>
+        <v>400</v>
       </c>
       <c r="H7" t="n">
-        <v>228.7711261016186</v>
+        <v>400</v>
       </c>
       <c r="I7" t="n">
-        <v>176.6334556201183</v>
+        <v>400</v>
       </c>
       <c r="J7" t="n">
         <v>35.26894883590776</v>
       </c>
       <c r="K7" t="n">
-        <v>288.520773801143</v>
+        <v>400</v>
       </c>
       <c r="L7" t="n">
         <v>400</v>
@@ -27879,10 +27879,10 @@
         <v>400</v>
       </c>
       <c r="S7" t="n">
-        <v>362.3734797028554</v>
+        <v>400</v>
       </c>
       <c r="T7" t="n">
-        <v>210.0245665062577</v>
+        <v>400</v>
       </c>
       <c r="U7" t="n">
         <v>400</v>
@@ -27891,13 +27891,13 @@
         <v>400</v>
       </c>
       <c r="W7" t="n">
-        <v>400</v>
+        <v>226.3728098387097</v>
       </c>
       <c r="X7" t="n">
-        <v>400</v>
+        <v>247.4436454301076</v>
       </c>
       <c r="Y7" t="n">
-        <v>400</v>
+        <v>287.4653528494624</v>
       </c>
     </row>
     <row r="8">
@@ -28007,7 +28007,7 @@
         <v>332.1680871864211</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>217.1263858913485</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -28034,7 +28034,7 @@
         <v>173.0792650904796</v>
       </c>
       <c r="R9" t="n">
-        <v>400</v>
+        <v>297.3202650713836</v>
       </c>
       <c r="S9" t="n">
         <v>400</v>
@@ -28046,7 +28046,7 @@
         <v>400</v>
       </c>
       <c r="V9" t="n">
-        <v>400</v>
+        <v>29.51066719152016</v>
       </c>
       <c r="W9" t="n">
         <v>400</v>
@@ -28055,7 +28055,7 @@
         <v>400</v>
       </c>
       <c r="Y9" t="n">
-        <v>143.3487109203867</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="10">
@@ -28065,7 +28065,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>287.1138003370787</v>
+        <v>299.4216474901395</v>
       </c>
       <c r="C10" t="n">
         <v>400</v>
@@ -28116,7 +28116,7 @@
         <v>400</v>
       </c>
       <c r="S10" t="n">
-        <v>374.6813268559163</v>
+        <v>362.3734797028554</v>
       </c>
       <c r="T10" t="n">
         <v>210.0245665062577</v>
@@ -28144,25 +28144,25 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="C11" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="D11" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="E11" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="F11" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="G11" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="H11" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="I11" t="n">
         <v>150.0811596826846</v>
@@ -28192,28 +28192,28 @@
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>219.5068074428802</v>
+        <v>250.8785988282945</v>
       </c>
       <c r="S11" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="T11" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="U11" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="V11" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="W11" t="n">
-        <v>225</v>
+        <v>247.5890086145856</v>
       </c>
       <c r="X11" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="Y11" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
     </row>
     <row r="12">
@@ -28223,76 +28223,76 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="C12" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="D12" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="E12" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="F12" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="G12" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="H12" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="I12" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="J12" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="K12" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="L12" t="n">
-        <v>19.11687125883913</v>
+        <v>251</v>
       </c>
       <c r="M12" t="n">
-        <v>225</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>225</v>
+        <v>244.1190264315981</v>
       </c>
       <c r="O12" t="n">
-        <v>225</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>225</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>225</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R12" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="S12" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="T12" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="U12" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="V12" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="W12" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="X12" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="Y12" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
     </row>
     <row r="13">
@@ -28302,76 +28302,76 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="C13" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="D13" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="E13" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="F13" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="G13" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="H13" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="I13" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="J13" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="K13" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="L13" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="M13" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="N13" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="O13" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="P13" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="Q13" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="R13" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="S13" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="T13" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="U13" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="V13" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="W13" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="X13" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="Y13" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
     </row>
     <row r="14">
@@ -28381,25 +28381,25 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="C14" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="D14" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="E14" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="F14" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="G14" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="H14" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="I14" t="n">
         <v>150.0811596826846</v>
@@ -28429,28 +28429,28 @@
         <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>219.5068074428802</v>
+        <v>247.4676074428803</v>
       </c>
       <c r="S14" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="T14" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="U14" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="V14" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="W14" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="X14" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="Y14" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
     </row>
     <row r="15">
@@ -28460,76 +28460,76 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="C15" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="D15" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="E15" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="F15" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="G15" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="H15" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="I15" t="n">
         <v>217.1263858913485</v>
       </c>
       <c r="J15" t="n">
-        <v>225</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>26.99048536749061</v>
+        <v>251</v>
       </c>
       <c r="L15" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="M15" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="N15" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="O15" t="n">
-        <v>225</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>225</v>
+        <v>26.99264054024918</v>
       </c>
       <c r="Q15" t="n">
-        <v>225</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R15" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="S15" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="T15" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="U15" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="V15" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="W15" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="X15" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="Y15" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
     </row>
     <row r="16">
@@ -28539,76 +28539,76 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="C16" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="D16" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="E16" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="F16" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="G16" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="H16" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="I16" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="J16" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="K16" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="L16" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="M16" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="N16" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="O16" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="P16" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="Q16" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="R16" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="S16" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="T16" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="U16" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="V16" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="W16" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="X16" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="Y16" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
     </row>
     <row r="17">
@@ -28618,28 +28618,28 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="C17" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="D17" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="E17" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="F17" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="G17" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="H17" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="I17" t="n">
-        <v>144.5879671255647</v>
+        <v>146.6701682972706</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -28666,28 +28666,28 @@
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>225</v>
+        <v>250.8785988282945</v>
       </c>
       <c r="S17" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="T17" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="U17" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="V17" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="W17" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="X17" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="Y17" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
     </row>
     <row r="18">
@@ -28697,76 +28697,76 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="C18" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="D18" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="E18" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="F18" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="G18" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="H18" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="I18" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="J18" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="K18" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="L18" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="M18" t="n">
-        <v>225</v>
+        <v>244.119026431598</v>
       </c>
       <c r="N18" t="n">
-        <v>225</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>19.11687125883898</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>225</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>225</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R18" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="S18" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="T18" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="U18" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="V18" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="W18" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="X18" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="Y18" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
     </row>
     <row r="19">
@@ -28776,76 +28776,76 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="C19" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="D19" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="E19" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="F19" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="G19" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="H19" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="I19" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="J19" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="K19" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="L19" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="M19" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="N19" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="O19" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="P19" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="Q19" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="R19" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="S19" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="T19" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="U19" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="V19" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="W19" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="X19" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="Y19" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
     </row>
     <row r="20">
@@ -28855,28 +28855,28 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="C20" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="D20" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="E20" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="F20" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="G20" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="H20" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="I20" t="n">
-        <v>150.0811596826846</v>
+        <v>146.6701682972706</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -28903,28 +28903,28 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>219.5068074428802</v>
+        <v>250.8785988282945</v>
       </c>
       <c r="S20" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="T20" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="U20" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="V20" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="W20" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="X20" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="Y20" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
     </row>
     <row r="21">
@@ -28934,76 +28934,76 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="C21" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="D21" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="E21" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="F21" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="G21" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="H21" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="I21" t="n">
-        <v>217.1263858913485</v>
+        <v>251</v>
       </c>
       <c r="J21" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="K21" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="L21" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="M21" t="n">
-        <v>26.99048536749062</v>
+        <v>244.119026431598</v>
       </c>
       <c r="N21" t="n">
-        <v>225</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>225</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>225</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>225</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R21" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="S21" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="T21" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="U21" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="V21" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="W21" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="X21" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="Y21" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
     </row>
     <row r="22">
@@ -29013,76 +29013,76 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="C22" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="D22" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="E22" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="F22" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="G22" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="H22" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="I22" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="J22" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="K22" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="L22" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="M22" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="N22" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="O22" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="P22" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="Q22" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="R22" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="S22" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="T22" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="U22" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="V22" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="W22" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="X22" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="Y22" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
     </row>
     <row r="23">
@@ -29092,28 +29092,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>219.5068074428801</v>
+        <v>251</v>
       </c>
       <c r="C23" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="D23" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="E23" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="F23" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="G23" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="H23" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="I23" t="n">
-        <v>150.0811596826846</v>
+        <v>146.6701682972706</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -29140,28 +29140,28 @@
         <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>225</v>
+        <v>250.8785988282945</v>
       </c>
       <c r="S23" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="T23" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="U23" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="V23" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="W23" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="X23" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="Y23" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
     </row>
     <row r="24">
@@ -29171,76 +29171,76 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="C24" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="D24" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="E24" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="F24" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="G24" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="H24" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="I24" t="n">
-        <v>217.1263858913485</v>
+        <v>251</v>
       </c>
       <c r="J24" t="n">
-        <v>225</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>78.91122027701095</v>
+        <v>251</v>
       </c>
       <c r="L24" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="M24" t="n">
-        <v>225</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>225</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
-        <v>225</v>
+        <v>166.1982915220774</v>
       </c>
       <c r="P24" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="Q24" t="n">
-        <v>173.0792650904796</v>
+        <v>251</v>
       </c>
       <c r="R24" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="S24" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="T24" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="U24" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="V24" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="W24" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="X24" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="Y24" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
     </row>
     <row r="25">
@@ -29250,76 +29250,76 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="C25" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="D25" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="E25" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="F25" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="G25" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="H25" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="I25" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="J25" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="K25" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="L25" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="M25" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="N25" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="O25" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="P25" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="Q25" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="R25" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="S25" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="T25" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="U25" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="V25" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="W25" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="X25" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
       <c r="Y25" t="n">
-        <v>225</v>
+        <v>251</v>
       </c>
     </row>
     <row r="26">
@@ -29350,7 +29350,7 @@
         <v>225</v>
       </c>
       <c r="I26" t="n">
-        <v>144.5879671255647</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -29398,7 +29398,7 @@
         <v>225</v>
       </c>
       <c r="Y26" t="n">
-        <v>225</v>
+        <v>219.5068074428801</v>
       </c>
     </row>
     <row r="27">
@@ -29429,10 +29429,10 @@
         <v>225</v>
       </c>
       <c r="I27" t="n">
-        <v>217.1263858913485</v>
+        <v>225</v>
       </c>
       <c r="J27" t="n">
-        <v>225</v>
+        <v>19.11687125883914</v>
       </c>
       <c r="K27" t="n">
         <v>225</v>
@@ -29444,7 +29444,7 @@
         <v>225</v>
       </c>
       <c r="N27" t="n">
-        <v>26.99048536749072</v>
+        <v>225</v>
       </c>
       <c r="O27" t="n">
         <v>225</v>
@@ -29569,7 +29569,7 @@
         <v>225</v>
       </c>
       <c r="C29" t="n">
-        <v>225</v>
+        <v>219.5068074428802</v>
       </c>
       <c r="D29" t="n">
         <v>225</v>
@@ -29614,7 +29614,7 @@
         <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>219.5068074428802</v>
+        <v>225</v>
       </c>
       <c r="S29" t="n">
         <v>225</v>
@@ -29672,7 +29672,7 @@
         <v>225</v>
       </c>
       <c r="K30" t="n">
-        <v>225</v>
+        <v>19.11687125883913</v>
       </c>
       <c r="L30" t="n">
         <v>225</v>
@@ -29687,7 +29687,7 @@
         <v>225</v>
       </c>
       <c r="P30" t="n">
-        <v>19.11687125883908</v>
+        <v>225</v>
       </c>
       <c r="Q30" t="n">
         <v>225</v>
@@ -29824,7 +29824,7 @@
         <v>225</v>
       </c>
       <c r="I32" t="n">
-        <v>144.5879671255647</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -29863,7 +29863,7 @@
         <v>225</v>
       </c>
       <c r="V32" t="n">
-        <v>225</v>
+        <v>219.5068074428799</v>
       </c>
       <c r="W32" t="n">
         <v>225</v>
@@ -29906,7 +29906,7 @@
         <v>225</v>
       </c>
       <c r="J33" t="n">
-        <v>225</v>
+        <v>19.11687125883914</v>
       </c>
       <c r="K33" t="n">
         <v>225</v>
@@ -29924,7 +29924,7 @@
         <v>225</v>
       </c>
       <c r="P33" t="n">
-        <v>19.11687125883908</v>
+        <v>225</v>
       </c>
       <c r="Q33" t="n">
         <v>225</v>
@@ -30088,7 +30088,7 @@
         <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>250.8785988282945</v>
+        <v>246.9132074428799</v>
       </c>
       <c r="S35" t="n">
         <v>350</v>
@@ -30106,7 +30106,7 @@
         <v>350</v>
       </c>
       <c r="X35" t="n">
-        <v>346.0346086145854</v>
+        <v>350</v>
       </c>
       <c r="Y35" t="n">
         <v>350</v>
@@ -30119,10 +30119,10 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>287.3222374745575</v>
+        <v>350</v>
       </c>
       <c r="C36" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="D36" t="n">
         <v>347.9376868977026</v>
@@ -30131,10 +30131,10 @@
         <v>342.6720972219126</v>
       </c>
       <c r="F36" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G36" t="n">
-        <v>325.7395358750273</v>
+        <v>252.6980156874617</v>
       </c>
       <c r="H36" t="n">
         <v>332.1680871864211</v>
@@ -30210,7 +30210,7 @@
         <v>350</v>
       </c>
       <c r="F37" t="n">
-        <v>350</v>
+        <v>342.2113306341341</v>
       </c>
       <c r="G37" t="n">
         <v>350</v>
@@ -30252,7 +30252,7 @@
         <v>350</v>
       </c>
       <c r="T37" t="n">
-        <v>342.2113306341342</v>
+        <v>350</v>
       </c>
       <c r="U37" t="n">
         <v>350</v>
@@ -30277,7 +30277,7 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>346.0346086145854</v>
+        <v>350</v>
       </c>
       <c r="C38" t="n">
         <v>350</v>
@@ -30328,7 +30328,7 @@
         <v>250.8785988282945</v>
       </c>
       <c r="S38" t="n">
-        <v>350</v>
+        <v>346.0346086145856</v>
       </c>
       <c r="T38" t="n">
         <v>350</v>
@@ -30359,13 +30359,13 @@
         <v>350</v>
       </c>
       <c r="C39" t="n">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="D39" t="n">
         <v>347.9376868977026</v>
       </c>
       <c r="E39" t="n">
-        <v>147.1207205878186</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F39" t="n">
         <v>339.6362423378769</v>
@@ -30377,7 +30377,7 @@
         <v>332.1680871864211</v>
       </c>
       <c r="I39" t="n">
-        <v>0</v>
+        <v>217.1263858913485</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -30410,7 +30410,7 @@
         <v>350</v>
       </c>
       <c r="T39" t="n">
-        <v>350</v>
+        <v>287.3222374745575</v>
       </c>
       <c r="U39" t="n">
         <v>350</v>
@@ -30444,7 +30444,7 @@
         <v>350</v>
       </c>
       <c r="E40" t="n">
-        <v>342.2113306341342</v>
+        <v>350</v>
       </c>
       <c r="F40" t="n">
         <v>350</v>
@@ -30498,7 +30498,7 @@
         <v>350</v>
       </c>
       <c r="W40" t="n">
-        <v>350</v>
+        <v>342.2113306341341</v>
       </c>
       <c r="X40" t="n">
         <v>350</v>
@@ -30535,7 +30535,7 @@
         <v>350</v>
       </c>
       <c r="I41" t="n">
-        <v>146.1157682972701</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -30562,7 +30562,7 @@
         <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>250.8785988282945</v>
+        <v>246.9132074428799</v>
       </c>
       <c r="S41" t="n">
         <v>350</v>
@@ -30611,7 +30611,7 @@
         <v>325.7395358750273</v>
       </c>
       <c r="H42" t="n">
-        <v>332.1680871864211</v>
+        <v>0</v>
       </c>
       <c r="I42" t="n">
         <v>217.1263858913485</v>
@@ -30641,10 +30641,10 @@
         <v>173.0792650904796</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>269.4903246609786</v>
       </c>
       <c r="S42" t="n">
-        <v>287.3222374745576</v>
+        <v>350</v>
       </c>
       <c r="T42" t="n">
         <v>350</v>
@@ -30757,7 +30757,7 @@
         <v>350</v>
       </c>
       <c r="D44" t="n">
-        <v>350</v>
+        <v>346.0346086145855</v>
       </c>
       <c r="E44" t="n">
         <v>350</v>
@@ -30805,7 +30805,7 @@
         <v>350</v>
       </c>
       <c r="T44" t="n">
-        <v>346.0346086145854</v>
+        <v>350</v>
       </c>
       <c r="U44" t="n">
         <v>350</v>
@@ -30833,7 +30833,7 @@
         <v>350</v>
       </c>
       <c r="C45" t="n">
-        <v>287.3222374745576</v>
+        <v>350</v>
       </c>
       <c r="D45" t="n">
         <v>347.9376868977026</v>
@@ -30842,7 +30842,7 @@
         <v>342.6720972219126</v>
       </c>
       <c r="F45" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G45" t="n">
         <v>325.7395358750273</v>
@@ -30881,13 +30881,13 @@
         <v>350</v>
       </c>
       <c r="S45" t="n">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="T45" t="n">
         <v>350</v>
       </c>
       <c r="U45" t="n">
-        <v>350</v>
+        <v>276.9584798124344</v>
       </c>
       <c r="V45" t="n">
         <v>350</v>
@@ -34883,13 +34883,13 @@
         <v>127.2747533519553</v>
       </c>
       <c r="D4" t="n">
-        <v>30.96294987442939</v>
+        <v>114.4637819444445</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>119.0190951630435</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>125.6171440322581</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -34931,16 +34931,16 @@
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>189.9754334937423</v>
       </c>
       <c r="U4" t="n">
-        <v>249.0416087255421</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>200.8296897837838</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>173.6271901612903</v>
+        <v>105.385983911557</v>
       </c>
       <c r="X4" t="n">
         <v>152.5563545698924</v>
@@ -34989,13 +34989,13 @@
         <v>369.4444444444445</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>385</v>
       </c>
       <c r="N5" t="n">
         <v>385</v>
       </c>
       <c r="O5" t="n">
-        <v>385</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
@@ -35114,34 +35114,34 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>112.8861996629213</v>
+        <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>127.2747533519553</v>
+        <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>114.4637819444445</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>119.0190951630435</v>
+        <v>60.32327647638356</v>
       </c>
       <c r="F7" t="n">
         <v>125.6171440322581</v>
       </c>
       <c r="G7" t="n">
-        <v>36.59397989877566</v>
+        <v>154.95612715847</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>171.2288738983814</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>223.3665443798817</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>111.479226198857</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -35165,10 +35165,10 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>37.62652029714457</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>189.9754334937423</v>
       </c>
       <c r="U7" t="n">
         <v>249.0416087255421</v>
@@ -35177,13 +35177,13 @@
         <v>200.8296897837838</v>
       </c>
       <c r="W7" t="n">
-        <v>173.6271901612903</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>152.5563545698924</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>112.5346471505376</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -35223,16 +35223,16 @@
         <v>385</v>
       </c>
       <c r="L8" t="n">
-        <v>369.4444444444445</v>
+        <v>385</v>
       </c>
       <c r="M8" t="n">
+        <v>369.4444444444443</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
         <v>385</v>
-      </c>
-      <c r="N8" t="n">
-        <v>385</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
@@ -35351,7 +35351,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>12.30784715306086</v>
       </c>
       <c r="C10" t="n">
         <v>127.2747533519553</v>
@@ -35402,7 +35402,7 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>12.30784715306086</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
         <v>0</v>
@@ -35457,25 +35457,25 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K11" t="n">
-        <v>716.8751175230996</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>916.1914086561842</v>
+        <v>382.9934426543497</v>
       </c>
       <c r="M11" t="n">
-        <v>516.0089179080152</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>519.902680094911</v>
+        <v>619.4144644189528</v>
       </c>
       <c r="O11" t="n">
-        <v>962.6692363858147</v>
+        <v>916</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>870.2908726334418</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -35530,31 +35530,31 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>7.873614108651466</v>
+        <v>33.87361410865147</v>
       </c>
       <c r="J12" t="n">
-        <v>350.2086062376757</v>
+        <v>376.2086062376757</v>
       </c>
       <c r="K12" t="n">
-        <v>416.1038546407913</v>
+        <v>442.1038546407913</v>
       </c>
       <c r="L12" t="n">
-        <v>293.2082466075261</v>
+        <v>525.0913753486871</v>
       </c>
       <c r="M12" t="n">
-        <v>311.9500421645043</v>
+        <v>86.95004216450428</v>
       </c>
       <c r="N12" t="n">
-        <v>359.6265501086548</v>
+        <v>378.7455765402529</v>
       </c>
       <c r="O12" t="n">
-        <v>466.4570219027464</v>
+        <v>241.4570219027464</v>
       </c>
       <c r="P12" t="n">
-        <v>338.6660045146532</v>
+        <v>113.6660045146532</v>
       </c>
       <c r="Q12" t="n">
-        <v>51.92073490952041</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -35603,16 +35603,16 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>5.956127158469968</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>22.22887389838138</v>
       </c>
       <c r="I13" t="n">
-        <v>48.36654437988173</v>
+        <v>74.36654437988173</v>
       </c>
       <c r="J13" t="n">
-        <v>189.7310511640922</v>
+        <v>215.7310511640922</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -35642,19 +35642,19 @@
         <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>14.97543349374229</v>
+        <v>40.97543349374229</v>
       </c>
       <c r="U13" t="n">
-        <v>74.04160872554206</v>
+        <v>100.0416087255421</v>
       </c>
       <c r="V13" t="n">
-        <v>25.82968978378381</v>
+        <v>51.82968978378381</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>24.62719016129032</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>3.556354569892449</v>
       </c>
       <c r="Y13" t="n">
         <v>0</v>
@@ -35691,13 +35691,13 @@
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>395.2617303410664</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>716.8751175230996</v>
+        <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>916.1914086561842</v>
+        <v>262.2462550874009</v>
       </c>
       <c r="M14" t="n">
         <v>516.0089179080152</v>
@@ -35706,10 +35706,10 @@
         <v>619.4144644189528</v>
       </c>
       <c r="O14" t="n">
-        <v>420.1280631196846</v>
+        <v>916</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>870.2908726334418</v>
       </c>
       <c r="Q14" t="n">
         <v>443.0293889420883</v>
@@ -35770,28 +35770,28 @@
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>350.2086062376757</v>
+        <v>125.2086062376757</v>
       </c>
       <c r="K15" t="n">
-        <v>218.0943400082819</v>
+        <v>442.1038546407913</v>
       </c>
       <c r="L15" t="n">
-        <v>499.091375348687</v>
+        <v>525.0913753486871</v>
       </c>
       <c r="M15" t="n">
-        <v>311.9500421645043</v>
+        <v>337.9500421645043</v>
       </c>
       <c r="N15" t="n">
-        <v>359.6265501086548</v>
+        <v>385.6265501086548</v>
       </c>
       <c r="O15" t="n">
-        <v>466.4570219027464</v>
+        <v>241.4570219027464</v>
       </c>
       <c r="P15" t="n">
-        <v>338.6660045146532</v>
+        <v>140.6586450549024</v>
       </c>
       <c r="Q15" t="n">
-        <v>51.92073490952041</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -35840,16 +35840,16 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>5.956127158469968</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>22.22887389838138</v>
       </c>
       <c r="I16" t="n">
-        <v>48.36654437988173</v>
+        <v>74.36654437988173</v>
       </c>
       <c r="J16" t="n">
-        <v>189.7310511640922</v>
+        <v>215.7310511640922</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -35879,19 +35879,19 @@
         <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>14.97543349374229</v>
+        <v>40.97543349374229</v>
       </c>
       <c r="U16" t="n">
-        <v>74.04160872554206</v>
+        <v>100.0416087255421</v>
       </c>
       <c r="V16" t="n">
-        <v>25.82968978378381</v>
+        <v>51.82968978378381</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>24.62719016129032</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>3.556354569892449</v>
       </c>
       <c r="Y16" t="n">
         <v>0</v>
@@ -35928,28 +35928,28 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>295.7499460170249</v>
+        <v>395.2617303410664</v>
       </c>
       <c r="K17" t="n">
-        <v>716.8751175230994</v>
+        <v>716.8751175230993</v>
       </c>
       <c r="L17" t="n">
-        <v>916.1914086561842</v>
+        <v>582.1183251312507</v>
       </c>
       <c r="M17" t="n">
-        <v>516.0089179080152</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
         <v>619.4144644189528</v>
       </c>
       <c r="O17" t="n">
-        <v>962.6692363858147</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>870.2908726334418</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>443.0293889420883</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -36004,31 +36004,31 @@
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>7.873614108651466</v>
+        <v>33.87361410865147</v>
       </c>
       <c r="J18" t="n">
-        <v>350.2086062376757</v>
+        <v>376.2086062376757</v>
       </c>
       <c r="K18" t="n">
-        <v>416.1038546407913</v>
+        <v>442.1038546407913</v>
       </c>
       <c r="L18" t="n">
-        <v>499.091375348687</v>
+        <v>525.0913753486871</v>
       </c>
       <c r="M18" t="n">
-        <v>311.9500421645043</v>
+        <v>331.0690685961023</v>
       </c>
       <c r="N18" t="n">
-        <v>359.6265501086548</v>
+        <v>134.6265501086548</v>
       </c>
       <c r="O18" t="n">
-        <v>260.5738931615854</v>
+        <v>241.4570219027464</v>
       </c>
       <c r="P18" t="n">
-        <v>338.6660045146532</v>
+        <v>113.6660045146532</v>
       </c>
       <c r="Q18" t="n">
-        <v>51.92073490952041</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -36077,16 +36077,16 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>5.956127158469968</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>22.22887389838138</v>
       </c>
       <c r="I19" t="n">
-        <v>48.36654437988173</v>
+        <v>74.36654437988173</v>
       </c>
       <c r="J19" t="n">
-        <v>189.7310511640922</v>
+        <v>215.7310511640922</v>
       </c>
       <c r="K19" t="n">
         <v>0</v>
@@ -36116,19 +36116,19 @@
         <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>14.97543349374229</v>
+        <v>40.97543349374229</v>
       </c>
       <c r="U19" t="n">
-        <v>74.04160872554206</v>
+        <v>100.0416087255421</v>
       </c>
       <c r="V19" t="n">
-        <v>25.82968978378381</v>
+        <v>51.82968978378381</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>24.62719016129032</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>3.556354569892449</v>
       </c>
       <c r="Y19" t="n">
         <v>0</v>
@@ -36168,10 +36168,10 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>716.8751175230993</v>
       </c>
       <c r="L20" t="n">
-        <v>220.2344802797121</v>
+        <v>66.10940722323539</v>
       </c>
       <c r="M20" t="n">
         <v>516.0089179080152</v>
@@ -36180,7 +36180,7 @@
         <v>619.4144644189528</v>
       </c>
       <c r="O20" t="n">
-        <v>962.6692363858147</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
         <v>870.2908726334418</v>
@@ -36241,31 +36241,31 @@
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>33.87361410865147</v>
       </c>
       <c r="J21" t="n">
-        <v>350.2086062376757</v>
+        <v>376.2086062376757</v>
       </c>
       <c r="K21" t="n">
-        <v>416.1038546407913</v>
+        <v>442.1038546407913</v>
       </c>
       <c r="L21" t="n">
-        <v>499.091375348687</v>
+        <v>525.0913753486871</v>
       </c>
       <c r="M21" t="n">
-        <v>113.9405275319949</v>
+        <v>331.0690685961023</v>
       </c>
       <c r="N21" t="n">
-        <v>359.6265501086548</v>
+        <v>134.6265501086548</v>
       </c>
       <c r="O21" t="n">
-        <v>466.4570219027464</v>
+        <v>241.4570219027464</v>
       </c>
       <c r="P21" t="n">
-        <v>338.6660045146532</v>
+        <v>113.6660045146532</v>
       </c>
       <c r="Q21" t="n">
-        <v>51.92073490952041</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -36314,16 +36314,16 @@
         <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>5.956127158469968</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>22.22887389838138</v>
       </c>
       <c r="I22" t="n">
-        <v>48.36654437988173</v>
+        <v>74.36654437988173</v>
       </c>
       <c r="J22" t="n">
-        <v>189.7310511640922</v>
+        <v>215.7310511640922</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
@@ -36353,19 +36353,19 @@
         <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>14.97543349374229</v>
+        <v>40.97543349374229</v>
       </c>
       <c r="U22" t="n">
-        <v>74.04160872554206</v>
+        <v>100.0416087255421</v>
       </c>
       <c r="V22" t="n">
-        <v>25.82968978378381</v>
+        <v>51.82968978378381</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>24.62719016129032</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>3.556354569892449</v>
       </c>
       <c r="Y22" t="n">
         <v>0</v>
@@ -36405,10 +36405,10 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K23" t="n">
-        <v>716.8751175230996</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>916.1914086561842</v>
+        <v>310.0139136884231</v>
       </c>
       <c r="M23" t="n">
         <v>516.0089179080152</v>
@@ -36417,13 +36417,13 @@
         <v>619.4144644189528</v>
       </c>
       <c r="O23" t="n">
-        <v>420.1280631196846</v>
+        <v>916</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>870.2908726334418</v>
       </c>
       <c r="Q23" t="n">
-        <v>443.0293889420883</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -36478,31 +36478,31 @@
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>33.87361410865147</v>
       </c>
       <c r="J24" t="n">
-        <v>350.2086062376757</v>
+        <v>125.2086062376757</v>
       </c>
       <c r="K24" t="n">
-        <v>270.0150749178023</v>
+        <v>442.1038546407913</v>
       </c>
       <c r="L24" t="n">
-        <v>499.091375348687</v>
+        <v>525.0913753486871</v>
       </c>
       <c r="M24" t="n">
-        <v>311.9500421645043</v>
+        <v>86.95004216450428</v>
       </c>
       <c r="N24" t="n">
-        <v>359.6265501086548</v>
+        <v>134.6265501086548</v>
       </c>
       <c r="O24" t="n">
-        <v>466.4570219027464</v>
+        <v>407.6553134248237</v>
       </c>
       <c r="P24" t="n">
-        <v>338.6660045146532</v>
+        <v>364.6660045146532</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>77.92073490952041</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -36551,16 +36551,16 @@
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>5.956127158469968</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>22.22887389838138</v>
       </c>
       <c r="I25" t="n">
-        <v>48.36654437988173</v>
+        <v>74.36654437988173</v>
       </c>
       <c r="J25" t="n">
-        <v>189.7310511640922</v>
+        <v>215.7310511640922</v>
       </c>
       <c r="K25" t="n">
         <v>0</v>
@@ -36590,19 +36590,19 @@
         <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>14.97543349374229</v>
+        <v>40.97543349374229</v>
       </c>
       <c r="U25" t="n">
-        <v>74.04160872554206</v>
+        <v>100.0416087255421</v>
       </c>
       <c r="V25" t="n">
-        <v>25.82968978378381</v>
+        <v>51.82968978378381</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>24.62719016129032</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>3.556354569892449</v>
       </c>
       <c r="Y25" t="n">
         <v>0</v>
@@ -36645,7 +36645,7 @@
         <v>716.8751175230996</v>
       </c>
       <c r="L26" t="n">
-        <v>466.0285991424271</v>
+        <v>916.1914086561842</v>
       </c>
       <c r="M26" t="n">
         <v>516.0089179080152</v>
@@ -36654,10 +36654,10 @@
         <v>619.4144644189528</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>420.1280631196846</v>
       </c>
       <c r="P26" t="n">
-        <v>870.2908726334418</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
         <v>443.0293889420883</v>
@@ -36715,10 +36715,10 @@
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>7.873614108651466</v>
       </c>
       <c r="J27" t="n">
-        <v>350.2086062376757</v>
+        <v>144.3254774965148</v>
       </c>
       <c r="K27" t="n">
         <v>416.1038546407913</v>
@@ -36730,7 +36730,7 @@
         <v>311.9500421645043</v>
       </c>
       <c r="N27" t="n">
-        <v>161.6170354761456</v>
+        <v>359.6265501086548</v>
       </c>
       <c r="O27" t="n">
         <v>466.4570219027464</v>
@@ -36876,25 +36876,25 @@
         <v>0</v>
       </c>
       <c r="J29" t="n">
-        <v>395.2617303410664</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>716.8751175230996</v>
+        <v>716.8751175230993</v>
       </c>
       <c r="L29" t="n">
-        <v>916.1914086561842</v>
+        <v>861.2903294834937</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>516.0089179080152</v>
       </c>
       <c r="N29" t="n">
         <v>619.4144644189528</v>
       </c>
       <c r="O29" t="n">
-        <v>936.1369810276999</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>870.2908726334418</v>
       </c>
       <c r="Q29" t="n">
         <v>443.0293889420883</v>
@@ -36958,7 +36958,7 @@
         <v>350.2086062376757</v>
       </c>
       <c r="K30" t="n">
-        <v>416.1038546407913</v>
+        <v>210.2207258996305</v>
       </c>
       <c r="L30" t="n">
         <v>499.091375348687</v>
@@ -36973,7 +36973,7 @@
         <v>466.4570219027464</v>
       </c>
       <c r="P30" t="n">
-        <v>132.7828757734923</v>
+        <v>338.6660045146532</v>
       </c>
       <c r="Q30" t="n">
         <v>51.92073490952041</v>
@@ -37192,7 +37192,7 @@
         <v>7.873614108651466</v>
       </c>
       <c r="J33" t="n">
-        <v>350.2086062376757</v>
+        <v>144.3254774965148</v>
       </c>
       <c r="K33" t="n">
         <v>416.1038546407913</v>
@@ -37210,7 +37210,7 @@
         <v>466.4570219027464</v>
       </c>
       <c r="P33" t="n">
-        <v>132.7828757734923</v>
+        <v>338.6660045146532</v>
       </c>
       <c r="Q33" t="n">
         <v>51.92073490952041</v>
@@ -37353,16 +37353,16 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K35" t="n">
-        <v>300.1141042229715</v>
+        <v>559</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="M35" t="n">
-        <v>516.0089179080152</v>
+        <v>0</v>
       </c>
       <c r="N35" t="n">
-        <v>559</v>
+        <v>257.1230221309866</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -37496,7 +37496,7 @@
         <v>69.01909516304346</v>
       </c>
       <c r="F37" t="n">
-        <v>75.61714403225807</v>
+        <v>67.82847466639221</v>
       </c>
       <c r="G37" t="n">
         <v>104.95612715847</v>
@@ -37538,7 +37538,7 @@
         <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>132.1867641278765</v>
+        <v>139.9754334937423</v>
       </c>
       <c r="U37" t="n">
         <v>199.0416087255421</v>
@@ -37587,28 +37587,28 @@
         <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>395.2617303410664</v>
+        <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="L38" t="n">
-        <v>0</v>
+        <v>559.0000000000001</v>
       </c>
       <c r="M38" t="n">
         <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>257.1230221309867</v>
+        <v>559</v>
       </c>
       <c r="O38" t="n">
-        <v>559</v>
+        <v>536.4141414141411</v>
       </c>
       <c r="P38" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>443.0293889420883</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
         <v>0</v>
@@ -37730,7 +37730,7 @@
         <v>64.46378194444452</v>
       </c>
       <c r="E40" t="n">
-        <v>61.23042579717762</v>
+        <v>69.01909516304346</v>
       </c>
       <c r="F40" t="n">
         <v>75.61714403225807</v>
@@ -37784,7 +37784,7 @@
         <v>150.8296897837838</v>
       </c>
       <c r="W40" t="n">
-        <v>123.6271901612903</v>
+        <v>115.8385207954244</v>
       </c>
       <c r="X40" t="n">
         <v>102.5563545698924</v>
@@ -37824,25 +37824,25 @@
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>395.2617303410664</v>
+        <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>559.0000000000001</v>
       </c>
       <c r="M41" t="n">
         <v>516.0089179080152</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>136.3758345640378</v>
       </c>
       <c r="O41" t="n">
-        <v>300.1141042229716</v>
+        <v>0</v>
       </c>
       <c r="P41" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
         <v>443.0293889420883</v>
@@ -38064,16 +38064,16 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K44" t="n">
-        <v>300.1141042229715</v>
+        <v>559</v>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>559</v>
       </c>
       <c r="M44" t="n">
-        <v>516.0089179080152</v>
+        <v>257.1230221309866</v>
       </c>
       <c r="N44" t="n">
-        <v>559</v>
+        <v>0</v>
       </c>
       <c r="O44" t="n">
         <v>0</v>
